--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EE2455-DB34-484F-99BA-FC050DDA0F30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF27532-D28E-BF40-9F07-E90B049F1D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
     <sheet name="dates" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$G$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$G$103</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="382">
   <si>
     <t>key</t>
   </si>
@@ -1129,6 +1129,51 @@
   </si>
   <si>
     <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. ‘Triadic’ refers to the sets of three technology options that are compared by each participant. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries in across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
+  </si>
+  <si>
+    <t>Magne</t>
+  </si>
+  <si>
+    <t>Neby</t>
+  </si>
+  <si>
+    <t>0000-0003-2098-7650</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>Notembaert</t>
+  </si>
+  <si>
+    <t>0000-0002-6266-2240</t>
+  </si>
+  <si>
+    <t>Marit</t>
+  </si>
+  <si>
+    <t>Jørgensen</t>
+  </si>
+  <si>
+    <t>0000-0002-6104-124X</t>
+  </si>
+  <si>
+    <t>Norwegian Institute of Bioeconomy Research</t>
+  </si>
+  <si>
+    <t>Mulatu</t>
+  </si>
+  <si>
+    <t>Kalkidan Ayele</t>
+  </si>
+  <si>
+    <t>Hesam</t>
+  </si>
+  <si>
+    <t>Mousavi</t>
+  </si>
+  <si>
+    <t>0000-0003-2615-756X</t>
   </si>
 </sst>
 </file>
@@ -1643,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -2447,16 +2492,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>283</v>
+        <v>373</v>
       </c>
       <c r="B42" t="s">
-        <v>263</v>
+        <v>374</v>
+      </c>
+      <c r="C42" t="s">
+        <v>375</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>127</v>
+        <v>376</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2464,19 +2512,16 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
-      </c>
-      <c r="C43" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
         <v>110</v>
       </c>
       <c r="E43" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2484,10 +2529,13 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>219</v>
+        <v>218</v>
+      </c>
+      <c r="C44" t="s">
+        <v>348</v>
       </c>
       <c r="D44" t="s">
         <v>110</v>
@@ -2501,22 +2549,16 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>265</v>
-      </c>
-      <c r="C45" t="s">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
       </c>
       <c r="E45" t="s">
-        <v>249</v>
-      </c>
-      <c r="F45" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2524,16 +2566,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s">
-        <v>266</v>
+        <v>265</v>
+      </c>
+      <c r="C46" t="s">
+        <v>349</v>
       </c>
       <c r="D46" t="s">
         <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>127</v>
+        <v>249</v>
+      </c>
+      <c r="F46" t="s">
+        <v>350</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2541,13 +2589,10 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
-      </c>
-      <c r="C47" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="D47" t="s">
         <v>110</v>
@@ -2561,19 +2606,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>365</v>
+        <v>126</v>
       </c>
       <c r="D48" t="s">
         <v>110</v>
       </c>
       <c r="E48" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2581,16 +2626,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>293</v>
+        <v>196</v>
       </c>
       <c r="B49" t="s">
-        <v>277</v>
+        <v>220</v>
+      </c>
+      <c r="C49" t="s">
+        <v>365</v>
       </c>
       <c r="D49" t="s">
         <v>110</v>
       </c>
       <c r="E49" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2598,19 +2646,16 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>95</v>
+        <v>293</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="D50" t="s">
         <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>309</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2618,16 +2663,19 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="B51" t="s">
-        <v>55</v>
+        <v>96</v>
+      </c>
+      <c r="C51" t="s">
+        <v>97</v>
       </c>
       <c r="D51" t="s">
         <v>110</v>
       </c>
       <c r="E51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2635,19 +2683,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>295</v>
+        <v>56</v>
       </c>
       <c r="B52" t="s">
-        <v>279</v>
-      </c>
-      <c r="C52" t="s">
-        <v>351</v>
+        <v>55</v>
       </c>
       <c r="D52" t="s">
         <v>110</v>
       </c>
       <c r="E52" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2655,19 +2700,19 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>131</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s">
-        <v>132</v>
+        <v>279</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>351</v>
       </c>
       <c r="D53" t="s">
         <v>110</v>
       </c>
       <c r="E53" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2675,19 +2720,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C54" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="D54" t="s">
         <v>110</v>
       </c>
       <c r="E54" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2695,19 +2740,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="C55" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D55" t="s">
         <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2715,16 +2760,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>361</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>362</v>
+        <v>134</v>
+      </c>
+      <c r="C56" t="s">
+        <v>135</v>
       </c>
       <c r="D56" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E56" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2732,16 +2780,16 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>287</v>
+        <v>361</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2749,16 +2797,16 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="B58" t="s">
-        <v>364</v>
+        <v>267</v>
       </c>
       <c r="D58" t="s">
         <v>110</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2766,19 +2814,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>179</v>
+        <v>363</v>
       </c>
       <c r="B59" t="s">
-        <v>180</v>
-      </c>
-      <c r="C59" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="D59" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E59" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2786,19 +2831,19 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B60" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="C60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D60" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E60" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2806,16 +2851,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>221</v>
+      </c>
+      <c r="C61" t="s">
+        <v>343</v>
       </c>
       <c r="D61" t="s">
         <v>110</v>
       </c>
       <c r="E61" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2823,19 +2871,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>268</v>
-      </c>
-      <c r="C62" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="D62" t="s">
         <v>110</v>
       </c>
       <c r="E62" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2843,19 +2888,19 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>259</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="C63" t="s">
-        <v>317</v>
+        <v>381</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="E63" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2863,19 +2908,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>288</v>
       </c>
       <c r="B64" t="s">
-        <v>104</v>
+        <v>268</v>
       </c>
       <c r="C64" t="s">
-        <v>103</v>
+        <v>344</v>
       </c>
       <c r="D64" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E64" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2883,19 +2928,16 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>74</v>
+        <v>378</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="D65" t="s">
         <v>110</v>
       </c>
       <c r="E65" t="s">
-        <v>49</v>
+        <v>245</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2903,19 +2945,19 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>80</v>
+        <v>259</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>316</v>
+      </c>
+      <c r="C66" t="s">
+        <v>317</v>
       </c>
       <c r="D66" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="E66" t="s">
-        <v>77</v>
-      </c>
-      <c r="F66" t="s">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2923,19 +2965,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>236</v>
+        <v>64</v>
       </c>
       <c r="B67" t="s">
-        <v>237</v>
+        <v>104</v>
       </c>
       <c r="C67" t="s">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E67" t="s">
-        <v>249</v>
+        <v>63</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -2943,16 +2985,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>298</v>
+        <v>74</v>
       </c>
       <c r="B68" t="s">
-        <v>269</v>
+        <v>75</v>
+      </c>
+      <c r="C68" t="s">
+        <v>345</v>
       </c>
       <c r="D68" t="s">
         <v>110</v>
       </c>
       <c r="E68" t="s">
-        <v>307</v>
+        <v>49</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2960,16 +3005,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>299</v>
+        <v>80</v>
       </c>
       <c r="B69" t="s">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="E69" t="s">
-        <v>181</v>
+        <v>77</v>
+      </c>
+      <c r="F69" t="s">
+        <v>82</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -2977,19 +3025,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="C70" t="s">
-        <v>321</v>
+        <v>346</v>
       </c>
       <c r="D70" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E70" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -2997,16 +3045,16 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>198</v>
+        <v>298</v>
       </c>
       <c r="B71" t="s">
-        <v>222</v>
+        <v>269</v>
       </c>
       <c r="D71" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>139</v>
+        <v>307</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3014,19 +3062,19 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>78</v>
+        <v>367</v>
       </c>
       <c r="B72" t="s">
-        <v>79</v>
+        <v>368</v>
       </c>
       <c r="C72" t="s">
-        <v>170</v>
+        <v>369</v>
       </c>
       <c r="D72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E72" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3034,39 +3082,36 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>289</v>
+        <v>370</v>
       </c>
       <c r="B73" t="s">
-        <v>271</v>
+        <v>371</v>
       </c>
       <c r="C73" t="s">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="D73" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E73" t="s">
-        <v>62</v>
+        <v>245</v>
       </c>
       <c r="G73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>86</v>
+        <v>299</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>167</v>
+        <v>270</v>
       </c>
       <c r="D74" t="s">
         <v>110</v>
       </c>
       <c r="E74" t="s">
-        <v>62</v>
+        <v>181</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3074,16 +3119,19 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="B75" t="s">
-        <v>278</v>
+        <v>320</v>
+      </c>
+      <c r="C75" t="s">
+        <v>321</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E75" t="s">
-        <v>310</v>
+        <v>181</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3091,19 +3139,16 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>290</v>
+        <v>198</v>
       </c>
       <c r="B76" t="s">
-        <v>272</v>
-      </c>
-      <c r="C76" t="s">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="D76" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E76" t="s">
-        <v>308</v>
+        <v>139</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3111,19 +3156,19 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="D77" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E77" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3131,36 +3176,39 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="B78" t="s">
-        <v>223</v>
+        <v>271</v>
       </c>
       <c r="C78" t="s">
-        <v>244</v>
+        <v>329</v>
       </c>
       <c r="D78" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E78" t="s">
-        <v>247</v>
+        <v>62</v>
       </c>
       <c r="G78">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>291</v>
+        <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>273</v>
+        <v>87</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="D79" t="s">
         <v>110</v>
       </c>
       <c r="E79" t="s">
-        <v>181</v>
+        <v>62</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3168,19 +3216,16 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B80" t="s">
-        <v>274</v>
-      </c>
-      <c r="C80" t="s">
-        <v>352</v>
+        <v>278</v>
       </c>
       <c r="D80" t="s">
         <v>110</v>
       </c>
       <c r="E80" t="s">
-        <v>77</v>
+        <v>310</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3188,19 +3233,19 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>199</v>
+        <v>290</v>
       </c>
       <c r="B81" t="s">
-        <v>224</v>
+        <v>272</v>
       </c>
       <c r="C81" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="D81" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>139</v>
+        <v>308</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3208,13 +3253,13 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="D82" t="s">
         <v>110</v>
@@ -3228,16 +3273,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B83" t="s">
-        <v>225</v>
+        <v>223</v>
+      </c>
+      <c r="C83" t="s">
+        <v>244</v>
       </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3245,16 +3293,13 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="B84" t="s">
-        <v>225</v>
-      </c>
-      <c r="C84" t="s">
-        <v>330</v>
+        <v>273</v>
       </c>
       <c r="D84" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E84" t="s">
         <v>181</v>
@@ -3265,16 +3310,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
+        <v>274</v>
+      </c>
+      <c r="C85" t="s">
+        <v>352</v>
       </c>
       <c r="D85" t="s">
         <v>110</v>
       </c>
       <c r="E85" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3282,19 +3330,19 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>59</v>
+        <v>199</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>224</v>
       </c>
       <c r="C86" t="s">
-        <v>168</v>
+        <v>353</v>
       </c>
       <c r="D86" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="E86" t="s">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3302,19 +3350,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>226</v>
+        <v>94</v>
       </c>
       <c r="C87" t="s">
-        <v>354</v>
+        <v>105</v>
       </c>
       <c r="D87" t="s">
         <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3322,19 +3370,16 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B88" t="s">
-        <v>227</v>
-      </c>
-      <c r="C88" t="s">
-        <v>331</v>
+        <v>225</v>
       </c>
       <c r="D88" t="s">
         <v>110</v>
       </c>
       <c r="E88" t="s">
-        <v>50</v>
+        <v>248</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3342,16 +3387,19 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>203</v>
+        <v>312</v>
       </c>
       <c r="B89" t="s">
-        <v>228</v>
+        <v>225</v>
+      </c>
+      <c r="C89" t="s">
+        <v>330</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E89" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -3359,19 +3407,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>204</v>
+        <v>114</v>
       </c>
       <c r="B90" t="s">
-        <v>229</v>
-      </c>
-      <c r="C90" t="s">
-        <v>332</v>
+        <v>115</v>
       </c>
       <c r="D90" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E90" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3379,16 +3424,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>297</v>
+        <v>59</v>
       </c>
       <c r="B91" t="s">
-        <v>275</v>
+        <v>60</v>
+      </c>
+      <c r="C91" t="s">
+        <v>168</v>
       </c>
       <c r="D91" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E91" t="s">
-        <v>308</v>
+        <v>49</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3396,19 +3444,19 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B92" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C92" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D92" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E92" t="s">
-        <v>240</v>
+        <v>181</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3416,16 +3464,19 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>311</v>
+        <v>202</v>
       </c>
       <c r="B93" t="s">
-        <v>276</v>
+        <v>227</v>
+      </c>
+      <c r="C93" t="s">
+        <v>331</v>
       </c>
       <c r="D93" t="s">
         <v>110</v>
       </c>
       <c r="E93" t="s">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -3433,19 +3484,16 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B94" t="s">
-        <v>231</v>
-      </c>
-      <c r="C94" t="s">
-        <v>355</v>
+        <v>228</v>
       </c>
       <c r="D94" t="s">
         <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>50</v>
+        <v>238</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -3453,19 +3501,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="B95" t="s">
-        <v>137</v>
+        <v>229</v>
       </c>
       <c r="C95" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="D95" t="s">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="E95" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3473,19 +3521,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>66</v>
+        <v>297</v>
       </c>
       <c r="B96" t="s">
-        <v>67</v>
-      </c>
-      <c r="C96" t="s">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="D96" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E96" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3493,16 +3538,19 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>296</v>
+        <v>205</v>
       </c>
       <c r="B97" t="s">
-        <v>280</v>
+        <v>230</v>
+      </c>
+      <c r="C97" t="s">
+        <v>333</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E97" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -3510,28 +3558,122 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>311</v>
+      </c>
+      <c r="B98" t="s">
+        <v>276</v>
+      </c>
+      <c r="D98" t="s">
+        <v>110</v>
+      </c>
+      <c r="E98" t="s">
+        <v>300</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>206</v>
+      </c>
+      <c r="B99" t="s">
+        <v>231</v>
+      </c>
+      <c r="C99" t="s">
+        <v>355</v>
+      </c>
+      <c r="D99" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" t="s">
+        <v>50</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>136</v>
+      </c>
+      <c r="B100" t="s">
+        <v>137</v>
+      </c>
+      <c r="C100" t="s">
+        <v>138</v>
+      </c>
+      <c r="D100" t="s">
+        <v>28</v>
+      </c>
+      <c r="E100" t="s">
+        <v>139</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>66</v>
+      </c>
+      <c r="B101" t="s">
+        <v>67</v>
+      </c>
+      <c r="C101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" t="s">
+        <v>143</v>
+      </c>
+      <c r="E101" t="s">
+        <v>63</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>296</v>
+      </c>
+      <c r="B102" t="s">
+        <v>280</v>
+      </c>
+      <c r="D102" t="s">
+        <v>110</v>
+      </c>
+      <c r="E102" t="s">
+        <v>309</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
         <v>53</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B103" t="s">
         <v>54</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C103" t="s">
         <v>169</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D103" t="s">
         <v>143</v>
       </c>
-      <c r="E98" t="s">
+      <c r="E103" t="s">
         <v>50</v>
       </c>
-      <c r="G98">
+      <c r="G103">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G98" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F97">
-    <sortCondition ref="B1:B97"/>
+  <autoFilter ref="A1:G103" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F102">
+    <sortCondition ref="B1:B102"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF27532-D28E-BF40-9F07-E90B049F1D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D4367-6F3A-5F45-9466-CBBBF7833F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,14 +21,14 @@
     <sheet name="dates" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$G$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$G$105</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="388">
   <si>
     <t>key</t>
   </si>
@@ -1174,6 +1174,24 @@
   </si>
   <si>
     <t>0000-0003-2615-756X</t>
+  </si>
+  <si>
+    <t>Roma Rani</t>
+  </si>
+  <si>
+    <t>Das</t>
+  </si>
+  <si>
+    <t>researcher</t>
+  </si>
+  <si>
+    <t>Abhishek</t>
+  </si>
+  <si>
+    <t>Rathore</t>
+  </si>
+  <si>
+    <t>0000-0001-6887-4095</t>
   </si>
 </sst>
 </file>
@@ -1688,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -2164,42 +2182,39 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>382</v>
       </c>
       <c r="B25" t="s">
-        <v>178</v>
-      </c>
-      <c r="C25" t="s">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>384</v>
       </c>
       <c r="E25" t="s">
         <v>77</v>
       </c>
-      <c r="F25" t="s">
-        <v>127</v>
-      </c>
       <c r="G25">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D26" t="s">
         <v>110</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>77</v>
+      </c>
+      <c r="F26" t="s">
+        <v>127</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2207,19 +2222,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
+        <v>256</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>339</v>
       </c>
       <c r="D27" t="s">
         <v>110</v>
       </c>
       <c r="E27" t="s">
-        <v>113</v>
+        <v>304</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2227,10 +2242,13 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
       </c>
       <c r="D28" t="s">
         <v>110</v>
@@ -2244,16 +2262,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="D29" t="s">
         <v>110</v>
       </c>
       <c r="E29" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2261,16 +2279,16 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D30" t="s">
         <v>110</v>
       </c>
       <c r="E30" t="s">
-        <v>300</v>
+        <v>62</v>
       </c>
       <c r="G30">
         <v>1</v>
@@ -2278,19 +2296,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
       <c r="B31" t="s">
-        <v>215</v>
-      </c>
-      <c r="C31" t="s">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="D31" t="s">
         <v>143</v>
       </c>
       <c r="E31" t="s">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2298,19 +2313,19 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>215</v>
       </c>
       <c r="C32" t="s">
-        <v>172</v>
+        <v>340</v>
       </c>
       <c r="D32" t="s">
         <v>143</v>
       </c>
       <c r="E32" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -2318,16 +2333,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>281</v>
+        <v>73</v>
       </c>
       <c r="B33" t="s">
-        <v>261</v>
+        <v>76</v>
+      </c>
+      <c r="C33" t="s">
+        <v>172</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E33" t="s">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -2335,19 +2353,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>191</v>
+        <v>281</v>
       </c>
       <c r="B34" t="s">
-        <v>233</v>
-      </c>
-      <c r="C34" t="s">
-        <v>232</v>
+        <v>261</v>
       </c>
       <c r="D34" t="s">
         <v>110</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>305</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2355,16 +2370,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>233</v>
+      </c>
+      <c r="C35" t="s">
+        <v>232</v>
       </c>
       <c r="D35" t="s">
         <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>306</v>
+        <v>50</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -2372,19 +2390,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>192</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>216</v>
-      </c>
-      <c r="C36" t="s">
-        <v>341</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
         <v>110</v>
       </c>
       <c r="E36" t="s">
-        <v>139</v>
+        <v>306</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2392,16 +2407,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>359</v>
+        <v>192</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>216</v>
+      </c>
+      <c r="C37" t="s">
+        <v>341</v>
       </c>
       <c r="D37" t="s">
         <v>110</v>
       </c>
       <c r="E37" t="s">
-        <v>358</v>
+        <v>139</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2409,19 +2427,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>193</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
-      </c>
-      <c r="C38" t="s">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="D38" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="E38" t="s">
-        <v>243</v>
+        <v>358</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2429,19 +2444,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>98</v>
+        <v>193</v>
       </c>
       <c r="B39" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>244</v>
       </c>
       <c r="D39" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>101</v>
+        <v>243</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2449,22 +2464,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>140</v>
+        <v>98</v>
       </c>
       <c r="B40" t="s">
-        <v>141</v>
+        <v>99</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E40" t="s">
-        <v>139</v>
-      </c>
-      <c r="F40" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2472,19 +2484,22 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>141</v>
       </c>
       <c r="C41" t="s">
-        <v>347</v>
+        <v>142</v>
       </c>
       <c r="D41" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="E41" t="s">
-        <v>249</v>
+        <v>139</v>
+      </c>
+      <c r="F41" t="s">
+        <v>50</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -2492,19 +2507,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>373</v>
+        <v>234</v>
       </c>
       <c r="B42" t="s">
-        <v>374</v>
+        <v>235</v>
       </c>
       <c r="C42" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E42" t="s">
-        <v>376</v>
+        <v>249</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2512,16 +2527,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>283</v>
+        <v>373</v>
       </c>
       <c r="B43" t="s">
-        <v>263</v>
+        <v>374</v>
+      </c>
+      <c r="C43" t="s">
+        <v>375</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>376</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2529,19 +2547,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>283</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
-      </c>
-      <c r="C44" t="s">
-        <v>348</v>
+        <v>263</v>
       </c>
       <c r="D44" t="s">
         <v>110</v>
       </c>
       <c r="E44" t="s">
-        <v>245</v>
+        <v>127</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2549,10 +2564,13 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>218</v>
+      </c>
+      <c r="C45" t="s">
+        <v>348</v>
       </c>
       <c r="D45" t="s">
         <v>110</v>
@@ -2566,22 +2584,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
-      </c>
-      <c r="C46" t="s">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
         <v>110</v>
       </c>
       <c r="E46" t="s">
-        <v>249</v>
-      </c>
-      <c r="F46" t="s">
-        <v>350</v>
+        <v>245</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2589,16 +2601,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>265</v>
+      </c>
+      <c r="C47" t="s">
+        <v>349</v>
       </c>
       <c r="D47" t="s">
         <v>110</v>
       </c>
       <c r="E47" t="s">
-        <v>127</v>
+        <v>249</v>
+      </c>
+      <c r="F47" t="s">
+        <v>350</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2606,13 +2624,10 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
-      </c>
-      <c r="C48" t="s">
-        <v>126</v>
+        <v>266</v>
       </c>
       <c r="D48" t="s">
         <v>110</v>
@@ -2626,19 +2641,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>196</v>
+        <v>128</v>
       </c>
       <c r="B49" t="s">
-        <v>220</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>365</v>
+        <v>126</v>
       </c>
       <c r="D49" t="s">
         <v>110</v>
       </c>
       <c r="E49" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2646,16 +2661,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>293</v>
+        <v>196</v>
       </c>
       <c r="B50" t="s">
-        <v>277</v>
+        <v>220</v>
+      </c>
+      <c r="C50" t="s">
+        <v>365</v>
       </c>
       <c r="D50" t="s">
         <v>110</v>
       </c>
       <c r="E50" t="s">
-        <v>309</v>
+        <v>246</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2663,19 +2681,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>293</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" t="s">
-        <v>97</v>
+        <v>277</v>
       </c>
       <c r="D51" t="s">
         <v>110</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>309</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2683,16 +2698,19 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>96</v>
+      </c>
+      <c r="C52" t="s">
+        <v>97</v>
       </c>
       <c r="D52" t="s">
         <v>110</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2700,19 +2718,16 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>295</v>
+        <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>279</v>
-      </c>
-      <c r="C53" t="s">
-        <v>351</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
         <v>110</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>61</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2720,19 +2735,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>295</v>
       </c>
       <c r="B54" t="s">
-        <v>132</v>
+        <v>279</v>
       </c>
       <c r="C54" t="s">
-        <v>130</v>
+        <v>351</v>
       </c>
       <c r="D54" t="s">
         <v>110</v>
       </c>
       <c r="E54" t="s">
-        <v>127</v>
+        <v>310</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2740,19 +2755,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>171</v>
+        <v>130</v>
       </c>
       <c r="D55" t="s">
         <v>110</v>
       </c>
       <c r="E55" t="s">
-        <v>62</v>
+        <v>127</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2760,19 +2775,19 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D56" t="s">
         <v>110</v>
       </c>
       <c r="E56" t="s">
-        <v>127</v>
+        <v>62</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2780,16 +2795,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>361</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>362</v>
+        <v>134</v>
+      </c>
+      <c r="C57" t="s">
+        <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2797,33 +2815,33 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>287</v>
+        <v>361</v>
       </c>
       <c r="B58" t="s">
-        <v>267</v>
+        <v>362</v>
       </c>
       <c r="D58" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E58" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>363</v>
+        <v>287</v>
       </c>
       <c r="B59" t="s">
-        <v>364</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
         <v>110</v>
       </c>
       <c r="E59" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2831,39 +2849,36 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>179</v>
+        <v>363</v>
       </c>
       <c r="B60" t="s">
-        <v>180</v>
-      </c>
-      <c r="C60" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="D60" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E60" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="B61" t="s">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D61" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E61" t="s">
-        <v>50</v>
+        <v>181</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2871,16 +2886,19 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>121</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
-        <v>122</v>
+        <v>221</v>
+      </c>
+      <c r="C62" t="s">
+        <v>343</v>
       </c>
       <c r="D62" t="s">
         <v>110</v>
       </c>
       <c r="E62" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2888,19 +2906,16 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>379</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>380</v>
-      </c>
-      <c r="C63" t="s">
-        <v>381</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E63" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2908,19 +2923,19 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>288</v>
+        <v>379</v>
       </c>
       <c r="B64" t="s">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="C64" t="s">
-        <v>344</v>
+        <v>381</v>
       </c>
       <c r="D64" t="s">
-        <v>110</v>
+        <v>144</v>
       </c>
       <c r="E64" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2928,16 +2943,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>378</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s">
-        <v>377</v>
+        <v>268</v>
+      </c>
+      <c r="C65" t="s">
+        <v>344</v>
       </c>
       <c r="D65" t="s">
         <v>110</v>
       </c>
       <c r="E65" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2945,19 +2963,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>259</v>
+        <v>378</v>
       </c>
       <c r="B66" t="s">
-        <v>316</v>
-      </c>
-      <c r="C66" t="s">
-        <v>317</v>
+        <v>377</v>
       </c>
       <c r="D66" t="s">
         <v>110</v>
       </c>
       <c r="E66" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2965,19 +2980,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="C67" t="s">
-        <v>103</v>
+        <v>317</v>
       </c>
       <c r="D67" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E67" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -2985,19 +3000,19 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
-        <v>345</v>
+        <v>103</v>
       </c>
       <c r="D68" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E68" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -3005,19 +3020,19 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>75</v>
+      </c>
+      <c r="C69" t="s">
+        <v>345</v>
       </c>
       <c r="D69" t="s">
-        <v>173</v>
+        <v>110</v>
       </c>
       <c r="E69" t="s">
-        <v>77</v>
-      </c>
-      <c r="F69" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3025,19 +3040,19 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>236</v>
+        <v>80</v>
       </c>
       <c r="B70" t="s">
-        <v>237</v>
-      </c>
-      <c r="C70" t="s">
-        <v>346</v>
+        <v>81</v>
       </c>
       <c r="D70" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="E70" t="s">
-        <v>249</v>
+        <v>77</v>
+      </c>
+      <c r="F70" t="s">
+        <v>82</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3045,16 +3060,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>298</v>
+        <v>236</v>
       </c>
       <c r="B71" t="s">
-        <v>269</v>
+        <v>237</v>
+      </c>
+      <c r="C71" t="s">
+        <v>346</v>
       </c>
       <c r="D71" t="s">
         <v>110</v>
       </c>
       <c r="E71" t="s">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3062,19 +3080,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>367</v>
+        <v>298</v>
       </c>
       <c r="B72" t="s">
-        <v>368</v>
-      </c>
-      <c r="C72" t="s">
-        <v>369</v>
+        <v>269</v>
       </c>
       <c r="D72" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="E72" t="s">
-        <v>49</v>
+        <v>307</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3082,19 +3097,19 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B73" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C73" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D73" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E73" t="s">
-        <v>245</v>
+        <v>49</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -3102,16 +3117,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>299</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s">
-        <v>270</v>
+        <v>371</v>
+      </c>
+      <c r="C74" t="s">
+        <v>372</v>
       </c>
       <c r="D74" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E74" t="s">
-        <v>181</v>
+        <v>245</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3119,16 +3137,13 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s">
-        <v>320</v>
-      </c>
-      <c r="C75" t="s">
-        <v>321</v>
+        <v>270</v>
       </c>
       <c r="D75" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E75" t="s">
         <v>181</v>
@@ -3139,16 +3154,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>198</v>
+        <v>319</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>320</v>
+      </c>
+      <c r="C76" t="s">
+        <v>321</v>
       </c>
       <c r="D76" t="s">
         <v>239</v>
       </c>
       <c r="E76" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3156,19 +3174,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
-      </c>
-      <c r="C77" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="D77" t="s">
-        <v>143</v>
+        <v>239</v>
       </c>
       <c r="E77" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3176,33 +3191,33 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>78</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>170</v>
+      </c>
+      <c r="D78" t="s">
+        <v>143</v>
+      </c>
+      <c r="E78" t="s">
+        <v>77</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
         <v>289</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>271</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>329</v>
-      </c>
-      <c r="D78" t="s">
-        <v>110</v>
-      </c>
-      <c r="E78" t="s">
-        <v>62</v>
-      </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
-        <v>86</v>
-      </c>
-      <c r="B79" t="s">
-        <v>87</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>167</v>
       </c>
       <c r="D79" t="s">
         <v>110</v>
@@ -3214,18 +3229,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>294</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>278</v>
+        <v>87</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="D80" t="s">
         <v>110</v>
       </c>
       <c r="E80" t="s">
-        <v>310</v>
+        <v>62</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3233,19 +3251,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B81" t="s">
-        <v>272</v>
-      </c>
-      <c r="C81" t="s">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="D81" t="s">
         <v>110</v>
       </c>
       <c r="E81" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3253,19 +3268,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>116</v>
+        <v>290</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>272</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>334</v>
       </c>
       <c r="D82" t="s">
         <v>110</v>
       </c>
       <c r="E82" t="s">
-        <v>63</v>
+        <v>308</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3273,19 +3288,19 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>117</v>
       </c>
       <c r="C83" t="s">
-        <v>244</v>
+        <v>118</v>
       </c>
       <c r="D83" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E83" t="s">
-        <v>247</v>
+        <v>63</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -3293,16 +3308,19 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>291</v>
+        <v>385</v>
       </c>
       <c r="B84" t="s">
-        <v>273</v>
+        <v>386</v>
+      </c>
+      <c r="C84" t="s">
+        <v>387</v>
       </c>
       <c r="D84" t="s">
-        <v>110</v>
+        <v>384</v>
       </c>
       <c r="E84" t="s">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="G84">
         <v>1</v>
@@ -3310,19 +3328,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="B85" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="C85" t="s">
-        <v>352</v>
+        <v>244</v>
       </c>
       <c r="D85" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E85" t="s">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3330,19 +3348,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>199</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s">
-        <v>224</v>
-      </c>
-      <c r="C86" t="s">
-        <v>353</v>
+        <v>273</v>
       </c>
       <c r="D86" t="s">
-        <v>239</v>
+        <v>110</v>
       </c>
       <c r="E86" t="s">
-        <v>139</v>
+        <v>181</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3350,19 +3365,19 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>93</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s">
-        <v>94</v>
+        <v>274</v>
       </c>
       <c r="C87" t="s">
-        <v>105</v>
+        <v>352</v>
       </c>
       <c r="D87" t="s">
         <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -3370,16 +3385,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B88" t="s">
-        <v>225</v>
+        <v>224</v>
+      </c>
+      <c r="C88" t="s">
+        <v>353</v>
       </c>
       <c r="D88" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
       <c r="E88" t="s">
-        <v>248</v>
+        <v>139</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3387,19 +3405,19 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>312</v>
+        <v>93</v>
       </c>
       <c r="B89" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="C89" t="s">
-        <v>330</v>
+        <v>105</v>
       </c>
       <c r="D89" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E89" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -3407,16 +3425,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>114</v>
+        <v>200</v>
       </c>
       <c r="B90" t="s">
-        <v>115</v>
+        <v>225</v>
       </c>
       <c r="D90" t="s">
         <v>110</v>
       </c>
       <c r="E90" t="s">
-        <v>113</v>
+        <v>248</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3424,19 +3442,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>59</v>
+        <v>312</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>225</v>
       </c>
       <c r="C91" t="s">
-        <v>168</v>
+        <v>330</v>
       </c>
       <c r="D91" t="s">
         <v>143</v>
       </c>
       <c r="E91" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3444,19 +3462,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
-        <v>226</v>
-      </c>
-      <c r="C92" t="s">
-        <v>354</v>
+        <v>115</v>
       </c>
       <c r="D92" t="s">
         <v>110</v>
       </c>
       <c r="E92" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3464,19 +3479,19 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
       <c r="B93" t="s">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>331</v>
+        <v>168</v>
       </c>
       <c r="D93" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E93" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G93">
         <v>1</v>
@@ -3484,16 +3499,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B94" t="s">
-        <v>228</v>
+        <v>226</v>
+      </c>
+      <c r="C94" t="s">
+        <v>354</v>
       </c>
       <c r="D94" t="s">
         <v>110</v>
       </c>
       <c r="E94" t="s">
-        <v>238</v>
+        <v>181</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -3501,19 +3519,19 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B95" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C95" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D95" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E95" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -3521,16 +3539,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>297</v>
+        <v>203</v>
       </c>
       <c r="B96" t="s">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="D96" t="s">
         <v>110</v>
       </c>
       <c r="E96" t="s">
-        <v>308</v>
+        <v>238</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3538,19 +3556,19 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B97" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D97" t="s">
         <v>143</v>
       </c>
       <c r="E97" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="G97">
         <v>1</v>
@@ -3558,16 +3576,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="B98" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D98" t="s">
         <v>110</v>
       </c>
       <c r="E98" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -3575,19 +3593,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B99" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C99" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="D99" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="E99" t="s">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -3595,19 +3613,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>311</v>
       </c>
       <c r="B100" t="s">
-        <v>137</v>
-      </c>
-      <c r="C100" t="s">
-        <v>138</v>
+        <v>276</v>
       </c>
       <c r="D100" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="E100" t="s">
-        <v>139</v>
+        <v>300</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -3615,19 +3630,19 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="B101" t="s">
-        <v>67</v>
+        <v>231</v>
       </c>
       <c r="C101" t="s">
-        <v>102</v>
+        <v>355</v>
       </c>
       <c r="D101" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E101" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -3635,16 +3650,19 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="B102" t="s">
-        <v>280</v>
+        <v>137</v>
+      </c>
+      <c r="C102" t="s">
+        <v>138</v>
       </c>
       <c r="D102" t="s">
-        <v>110</v>
+        <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>309</v>
+        <v>139</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -3652,28 +3670,65 @@
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B103" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C103" t="s">
-        <v>169</v>
+        <v>102</v>
       </c>
       <c r="D103" t="s">
         <v>143</v>
       </c>
       <c r="E103" t="s">
+        <v>63</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>296</v>
+      </c>
+      <c r="B104" t="s">
+        <v>280</v>
+      </c>
+      <c r="D104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E104" t="s">
+        <v>309</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>53</v>
+      </c>
+      <c r="B105" t="s">
+        <v>54</v>
+      </c>
+      <c r="C105" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" t="s">
+        <v>143</v>
+      </c>
+      <c r="E105" t="s">
         <v>50</v>
       </c>
-      <c r="G103">
+      <c r="G105">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G103" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F102">
-    <sortCondition ref="B1:B102"/>
+  <autoFilter ref="A1:G105" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F104">
+    <sortCondition ref="B1:B104"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0D4367-6F3A-5F45-9466-CBBBF7833F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E184C351-FD1E-0F49-A6DB-D349916A83C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -285,9 +285,6 @@
     <t>INV-009649</t>
   </si>
   <si>
-    <t>2025-09-06</t>
-  </si>
-  <si>
     <t>Patrick Obia</t>
   </si>
   <si>
@@ -306,9 +303,6 @@
     <t>https://ror.org/00e0ttj68</t>
   </si>
   <si>
-    <t>v1</t>
-  </si>
-  <si>
     <t>Abdul</t>
   </si>
   <si>
@@ -1128,9 +1122,6 @@
     <t>0000-0001-6353-960X</t>
   </si>
   <si>
-    <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. ‘Triadic’ refers to the sets of three technology options that are compared by each participant. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries in across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
-  </si>
-  <si>
     <t>Magne</t>
   </si>
   <si>
@@ -1192,6 +1183,15 @@
   </si>
   <si>
     <t>0000-0001-6887-4095</t>
+  </si>
+  <si>
+    <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. ‘Triadic’ refers to the sets of three technology options that are compared by each participant. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
+  </si>
+  <si>
+    <t>2025-09-10</t>
+  </si>
+  <si>
+    <t>v0.9</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1621,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1629,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1637,7 +1637,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>85</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1653,7 +1653,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1685,7 +1685,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1693,7 +1693,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -1738,7 +1738,7 @@
         <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -1786,16 +1786,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
         <v>356</v>
-      </c>
-      <c r="B4" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4" t="s">
-        <v>358</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1803,16 +1803,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
         <v>301</v>
-      </c>
-      <c r="B5" t="s">
-        <v>302</v>
-      </c>
-      <c r="D5" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" t="s">
-        <v>303</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1820,16 +1820,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -1837,13 +1837,13 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
@@ -1854,19 +1854,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
         <v>123</v>
       </c>
-      <c r="B8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" t="s">
-        <v>125</v>
-      </c>
       <c r="D8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1880,10 +1880,10 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
@@ -1894,19 +1894,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1914,16 +1914,16 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
         <v>50</v>
@@ -1934,16 +1934,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
@@ -1954,19 +1954,19 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1974,19 +1974,19 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -2000,10 +2000,10 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" t="s">
         <v>63</v>
@@ -2014,16 +2014,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -2031,19 +2031,19 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -2051,13 +2051,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>62</v>
@@ -2068,19 +2068,19 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2088,16 +2088,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2105,19 +2105,19 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -2125,16 +2125,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B22" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C22" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D22" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E22" t="s">
         <v>50</v>
@@ -2145,16 +2145,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -2171,7 +2171,7 @@
         <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -2182,13 +2182,13 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B25" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D25" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E25" t="s">
         <v>77</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C26" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -2222,19 +2222,19 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B27" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C27" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2242,19 +2242,19 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>105</v>
+      </c>
+      <c r="B28" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" t="s">
         <v>107</v>
       </c>
-      <c r="B28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
-      </c>
       <c r="D28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2262,16 +2262,16 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" t="s">
         <v>111</v>
-      </c>
-      <c r="B29" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" t="s">
-        <v>110</v>
-      </c>
-      <c r="E29" t="s">
-        <v>113</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -2279,13 +2279,13 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E30" t="s">
         <v>62</v>
@@ -2296,16 +2296,16 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D31" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E31" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -2313,16 +2313,16 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C32" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -2339,10 +2339,10 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
         <v>77</v>
@@ -2353,16 +2353,16 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -2370,16 +2370,16 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C35" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
@@ -2390,16 +2390,16 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B36" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -2407,19 +2407,19 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D37" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E37" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -2427,16 +2427,16 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -2444,19 +2444,19 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B39" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C39" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -2464,19 +2464,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>96</v>
+      </c>
+      <c r="B40" t="s">
+        <v>97</v>
+      </c>
+      <c r="C40" t="s">
         <v>98</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
+        <v>108</v>
+      </c>
+      <c r="E40" t="s">
         <v>99</v>
-      </c>
-      <c r="C40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D40" t="s">
-        <v>110</v>
-      </c>
-      <c r="E40" t="s">
-        <v>101</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -2484,19 +2484,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>138</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" t="s">
         <v>140</v>
       </c>
-      <c r="B41" t="s">
-        <v>141</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>142</v>
       </c>
-      <c r="D41" t="s">
-        <v>144</v>
-      </c>
       <c r="E41" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F41" t="s">
         <v>50</v>
@@ -2507,19 +2507,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C42" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E42" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -2527,19 +2527,19 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>370</v>
+      </c>
+      <c r="B43" t="s">
+        <v>371</v>
+      </c>
+      <c r="C43" t="s">
+        <v>372</v>
+      </c>
+      <c r="D43" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" t="s">
         <v>373</v>
-      </c>
-      <c r="B43" t="s">
-        <v>374</v>
-      </c>
-      <c r="C43" t="s">
-        <v>375</v>
-      </c>
-      <c r="D43" t="s">
-        <v>143</v>
-      </c>
-      <c r="E43" t="s">
-        <v>376</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -2547,16 +2547,16 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B44" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -2564,19 +2564,19 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B45" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -2584,16 +2584,16 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D46" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E46" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D47" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E47" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F47" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2624,16 +2624,16 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D48" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2641,19 +2641,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D49" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E49" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2661,19 +2661,19 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B50" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C50" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E50" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2681,16 +2681,16 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B51" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D51" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2698,16 +2698,16 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
         <v>95</v>
       </c>
-      <c r="B52" t="s">
-        <v>96</v>
-      </c>
-      <c r="C52" t="s">
-        <v>97</v>
-      </c>
       <c r="D52" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E52" t="s">
         <v>63</v>
@@ -2724,7 +2724,7 @@
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E53" t="s">
         <v>61</v>
@@ -2735,19 +2735,19 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B54" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C54" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E54" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2755,19 +2755,19 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B55" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C55" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E55" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2781,10 +2781,10 @@
         <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D56" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
         <v>62</v>
@@ -2795,19 +2795,19 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" t="s">
         <v>133</v>
       </c>
-      <c r="B57" t="s">
-        <v>134</v>
-      </c>
-      <c r="C57" t="s">
-        <v>135</v>
-      </c>
       <c r="D57" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E57" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2815,13 +2815,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B58" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D58" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E58" t="s">
         <v>77</v>
@@ -2832,16 +2832,16 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D59" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E59" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2849,13 +2849,13 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D60" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E60" t="s">
         <v>77</v>
@@ -2866,19 +2866,19 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>177</v>
+      </c>
+      <c r="B61" t="s">
+        <v>178</v>
+      </c>
+      <c r="C61" t="s">
+        <v>340</v>
+      </c>
+      <c r="D61" t="s">
+        <v>141</v>
+      </c>
+      <c r="E61" t="s">
         <v>179</v>
-      </c>
-      <c r="B61" t="s">
-        <v>180</v>
-      </c>
-      <c r="C61" t="s">
-        <v>342</v>
-      </c>
-      <c r="D61" t="s">
-        <v>143</v>
-      </c>
-      <c r="E61" t="s">
-        <v>181</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2886,16 +2886,16 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B62" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C62" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D62" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E62" t="s">
         <v>50</v>
@@ -2906,13 +2906,13 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D63" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E63" t="s">
         <v>63</v>
@@ -2923,16 +2923,16 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B64" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C64" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D64" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
@@ -2943,19 +2943,19 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B65" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C65" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D65" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E65" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2963,16 +2963,16 @@
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B66" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D66" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E66" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2980,19 +2980,19 @@
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B67" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C67" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D67" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E67" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -3003,13 +3003,13 @@
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C68" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D68" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
         <v>63</v>
@@ -3026,10 +3026,10 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D69" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E69" t="s">
         <v>49</v>
@@ -3046,7 +3046,7 @@
         <v>81</v>
       </c>
       <c r="D70" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E70" t="s">
         <v>77</v>
@@ -3060,19 +3060,19 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B71" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C71" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D71" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E71" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -3080,16 +3080,16 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D72" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E72" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -3097,16 +3097,16 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B73" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C73" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D73" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E73" t="s">
         <v>49</v>
@@ -3117,19 +3117,19 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B74" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C74" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D74" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E74" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -3137,16 +3137,16 @@
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E75" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3154,19 +3154,19 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
+        <v>317</v>
+      </c>
+      <c r="B76" t="s">
+        <v>318</v>
+      </c>
+      <c r="C76" t="s">
         <v>319</v>
       </c>
-      <c r="B76" t="s">
-        <v>320</v>
-      </c>
-      <c r="C76" t="s">
-        <v>321</v>
-      </c>
       <c r="D76" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E76" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -3174,16 +3174,16 @@
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B77" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D77" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E77" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3197,10 +3197,10 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D78" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E78" t="s">
         <v>77</v>
@@ -3211,16 +3211,16 @@
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B79" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C79" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D79" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E79" t="s">
         <v>62</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>85</v>
+      </c>
+      <c r="B80" t="s">
         <v>86</v>
       </c>
-      <c r="B80" t="s">
-        <v>87</v>
-      </c>
       <c r="C80" s="6" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E80" t="s">
         <v>62</v>
@@ -3251,16 +3251,16 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B81" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D81" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E81" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -3268,19 +3268,19 @@
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B82" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C82" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D82" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E82" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -3288,16 +3288,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>114</v>
+      </c>
+      <c r="B83" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" t="s">
         <v>116</v>
       </c>
-      <c r="B83" t="s">
-        <v>117</v>
-      </c>
-      <c r="C83" t="s">
-        <v>118</v>
-      </c>
       <c r="D83" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E83" t="s">
         <v>63</v>
@@ -3308,16 +3308,16 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B84" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C84" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D84" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
@@ -3328,19 +3328,19 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C85" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D85" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E85" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -3348,16 +3348,16 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B86" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D86" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E86" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -3365,16 +3365,16 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B87" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C87" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D87" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E87" t="s">
         <v>77</v>
@@ -3385,19 +3385,19 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C88" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D88" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E88" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3405,16 +3405,16 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B89" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C89" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E89" t="s">
         <v>63</v>
@@ -3425,16 +3425,16 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B90" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E90" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G90">
         <v>1</v>
@@ -3442,19 +3442,19 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C91" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D91" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E91" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G91">
         <v>1</v>
@@ -3462,16 +3462,16 @@
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B92" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E92" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -3485,10 +3485,10 @@
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D93" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E93" t="s">
         <v>49</v>
@@ -3499,19 +3499,19 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B94" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C94" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D94" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E94" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G94">
         <v>1</v>
@@ -3519,16 +3519,16 @@
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B95" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D95" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
@@ -3539,16 +3539,16 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B96" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D96" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E96" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G96">
         <v>1</v>
@@ -3556,16 +3556,16 @@
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B97" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C97" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D97" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E97" t="s">
         <v>62</v>
@@ -3576,16 +3576,16 @@
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B98" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D98" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E98" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G98">
         <v>1</v>
@@ -3593,19 +3593,19 @@
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B99" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C99" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D99" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E99" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G99">
         <v>1</v>
@@ -3613,16 +3613,16 @@
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B100" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D100" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E100" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G100">
         <v>1</v>
@@ -3630,16 +3630,16 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B101" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C101" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D101" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
@@ -3650,19 +3650,19 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>134</v>
+      </c>
+      <c r="B102" t="s">
+        <v>135</v>
+      </c>
+      <c r="C102" t="s">
         <v>136</v>
-      </c>
-      <c r="B102" t="s">
-        <v>137</v>
-      </c>
-      <c r="C102" t="s">
-        <v>138</v>
       </c>
       <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G102">
         <v>1</v>
@@ -3676,10 +3676,10 @@
         <v>67</v>
       </c>
       <c r="C103" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D103" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E103" t="s">
         <v>63</v>
@@ -3690,16 +3690,16 @@
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B104" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D104" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E104" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -3713,10 +3713,10 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E105" t="s">
         <v>50</v>
@@ -3745,107 +3745,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -3925,13 +3925,13 @@
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" t="s">
         <v>89</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
       </c>
       <c r="D5">
         <v>81260859</v>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E184C351-FD1E-0F49-A6DB-D349916A83C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A388A5C2-D181-A647-9D40-D6DD409D7FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A388A5C2-D181-A647-9D40-D6DD409D7FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F74141-5EC8-D641-A54B-B4CE2A02778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="30720" windowHeight="17200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10600" yWindow="1020" windowWidth="20120" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -21,14 +21,14 @@
     <sheet name="dates" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$G$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$J$105</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="391">
   <si>
     <t>key</t>
   </si>
@@ -297,9 +297,6 @@
     <t>BMZ</t>
   </si>
   <si>
-    <t>Choose, Grow, Thrive: Using citizen science in expanding West Africa's food basket with African vegetables to tackle malnutrition (BMZ-CGT)”</t>
-  </si>
-  <si>
     <t>https://ror.org/00e0ttj68</t>
   </si>
   <si>
@@ -612,9 +609,6 @@
     <t>Fadhili</t>
   </si>
   <si>
-    <t>Basazen </t>
-  </si>
-  <si>
     <t>Dejene K.</t>
   </si>
   <si>
@@ -642,9 +636,6 @@
     <t>Hale Ann</t>
   </si>
   <si>
-    <t>Jacob </t>
-  </si>
-  <si>
     <t>Aguilar</t>
   </si>
   <si>
@@ -1192,6 +1183,24 @@
   </si>
   <si>
     <t>v0.9</t>
+  </si>
+  <si>
+    <t>Choose Grow Thrive: Using citizen science in expanding West Africa's food basket with African vegetables to tackle malnutrition (BMZ-CGT)”</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>Basazen</t>
+  </si>
+  <si>
+    <t>Jacob</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1630,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1629,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1637,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1653,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1677,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1693,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1706,19 +1715,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="6" max="9" width="13.5" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1738,10 +1747,19 @@
         <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -1760,11 +1778,11 @@
       <c r="F2" t="s">
         <v>49</v>
       </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -1780,99 +1798,99 @@
       <c r="E3" t="s">
         <v>50</v>
       </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>356</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>301</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" t="s">
+        <v>245</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" t="s">
         <v>249</v>
       </c>
-      <c r="B6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" t="s">
-        <v>248</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>251</v>
-      </c>
-      <c r="B7" t="s">
-        <v>252</v>
-      </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
         <v>62</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" t="s">
         <v>121</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>122</v>
       </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -1880,119 +1898,119 @@
         <v>69</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>63</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" t="s">
+        <v>202</v>
+      </c>
+      <c r="C10" t="s">
+        <v>323</v>
+      </c>
+      <c r="D10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" t="s">
+        <v>233</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
         <v>180</v>
       </c>
-      <c r="B10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C10" t="s">
-        <v>326</v>
-      </c>
-      <c r="D10" t="s">
-        <v>108</v>
-      </c>
-      <c r="E10" t="s">
-        <v>236</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>181</v>
-      </c>
       <c r="B11" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>50</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C12" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E13" t="s">
-        <v>243</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B14" t="s">
+        <v>310</v>
+      </c>
+      <c r="C14" t="s">
         <v>313</v>
       </c>
-      <c r="C14" t="s">
-        <v>316</v>
-      </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E14" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -2000,167 +2018,167 @@
         <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>63</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B16" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" t="s">
+        <v>233</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
         <v>183</v>
       </c>
-      <c r="B16" t="s">
-        <v>208</v>
-      </c>
-      <c r="D16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" t="s">
-        <v>236</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>184</v>
-      </c>
       <c r="B17" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E17" t="s">
-        <v>137</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
         <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
         <v>62</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>184</v>
+      </c>
+      <c r="B19" t="s">
+        <v>207</v>
+      </c>
+      <c r="C19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E19" t="s">
+        <v>235</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>185</v>
       </c>
-      <c r="B19" t="s">
-        <v>210</v>
-      </c>
-      <c r="C19" t="s">
-        <v>323</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>245</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" t="s">
         <v>237</v>
-      </c>
-      <c r="E19" t="s">
-        <v>238</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>248</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>187</v>
-      </c>
-      <c r="B21" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" t="s">
-        <v>240</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>239</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+        <v>236</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B22" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C22" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D22" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E22" t="s">
         <v>50</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" t="s">
         <v>117</v>
       </c>
-      <c r="B23" t="s">
-        <v>118</v>
-      </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>51</v>
       </c>
@@ -2171,167 +2189,167 @@
         <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B25" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D25" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E25" t="s">
         <v>77</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" t="s">
         <v>175</v>
       </c>
-      <c r="B26" t="s">
-        <v>176</v>
-      </c>
       <c r="C26" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
       </c>
       <c r="F26" t="s">
-        <v>125</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" t="s">
+        <v>334</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
+        <v>299</v>
+      </c>
+      <c r="J27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>108</v>
+      </c>
+      <c r="B29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>252</v>
+      </c>
+      <c r="B30" t="s">
         <v>253</v>
       </c>
-      <c r="B27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C27" t="s">
-        <v>337</v>
-      </c>
-      <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" t="s">
-        <v>302</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>105</v>
-      </c>
-      <c r="B28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C28" t="s">
-        <v>107</v>
-      </c>
-      <c r="D28" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" t="s">
-        <v>111</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" t="s">
-        <v>111</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>255</v>
-      </c>
-      <c r="B30" t="s">
-        <v>256</v>
-      </c>
       <c r="D30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E30" t="s">
         <v>62</v>
       </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E31" t="s">
-        <v>298</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C32" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>73</v>
       </c>
@@ -2339,384 +2357,384 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E33" t="s">
         <v>77</v>
       </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
-        <v>303</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="J34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C35" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
       </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B36" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>304</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+      <c r="J36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" t="s">
+        <v>211</v>
+      </c>
+      <c r="C37" t="s">
+        <v>336</v>
+      </c>
+      <c r="D37" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" t="s">
+        <v>136</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>354</v>
+      </c>
+      <c r="B38" t="s">
+        <v>355</v>
+      </c>
+      <c r="D38" t="s">
+        <v>107</v>
+      </c>
+      <c r="E38" t="s">
+        <v>353</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>190</v>
       </c>
-      <c r="B37" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" t="s">
-        <v>339</v>
-      </c>
-      <c r="D37" t="s">
-        <v>108</v>
-      </c>
-      <c r="E37" t="s">
-        <v>137</v>
-      </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>357</v>
-      </c>
-      <c r="B38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D38" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" t="s">
-        <v>356</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>191</v>
-      </c>
       <c r="B39" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C39" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>241</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+        <v>238</v>
+      </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>95</v>
+      </c>
+      <c r="B40" t="s">
         <v>96</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>97</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>107</v>
+      </c>
+      <c r="E40" t="s">
         <v>98</v>
       </c>
-      <c r="D40" t="s">
-        <v>108</v>
-      </c>
-      <c r="E40" t="s">
-        <v>99</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>137</v>
+      </c>
+      <c r="B41" t="s">
         <v>138</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>139</v>
       </c>
-      <c r="C41" t="s">
-        <v>140</v>
-      </c>
       <c r="D41" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F41" t="s">
         <v>50</v>
       </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C42" t="s">
+        <v>342</v>
+      </c>
+      <c r="D42" t="s">
+        <v>107</v>
+      </c>
+      <c r="E42" t="s">
+        <v>244</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>367</v>
+      </c>
+      <c r="B43" t="s">
+        <v>368</v>
+      </c>
+      <c r="C43" t="s">
+        <v>369</v>
+      </c>
+      <c r="D43" t="s">
+        <v>140</v>
+      </c>
+      <c r="E43" t="s">
+        <v>370</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>278</v>
+      </c>
+      <c r="B44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B45" t="s">
+        <v>213</v>
+      </c>
+      <c r="C45" t="s">
+        <v>343</v>
+      </c>
+      <c r="D45" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" t="s">
+        <v>240</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" t="s">
+        <v>214</v>
+      </c>
+      <c r="D46" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" t="s">
+        <v>240</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>280</v>
+      </c>
+      <c r="B47" t="s">
+        <v>260</v>
+      </c>
+      <c r="C47" t="s">
+        <v>344</v>
+      </c>
+      <c r="D47" t="s">
+        <v>107</v>
+      </c>
+      <c r="E47" t="s">
+        <v>244</v>
+      </c>
+      <c r="F47" t="s">
         <v>345</v>
       </c>
-      <c r="D42" t="s">
-        <v>108</v>
-      </c>
-      <c r="E42" t="s">
-        <v>247</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>370</v>
-      </c>
-      <c r="B43" t="s">
-        <v>371</v>
-      </c>
-      <c r="C43" t="s">
-        <v>372</v>
-      </c>
-      <c r="D43" t="s">
-        <v>141</v>
-      </c>
-      <c r="E43" t="s">
-        <v>373</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+      <c r="J47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
         <v>281</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B48" t="s">
         <v>261</v>
       </c>
-      <c r="D44" t="s">
-        <v>108</v>
-      </c>
-      <c r="E44" t="s">
+      <c r="D48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E48" t="s">
+        <v>124</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
         <v>125</v>
       </c>
-      <c r="G44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>192</v>
-      </c>
-      <c r="B45" t="s">
-        <v>216</v>
-      </c>
-      <c r="C45" t="s">
-        <v>346</v>
-      </c>
-      <c r="D45" t="s">
-        <v>108</v>
-      </c>
-      <c r="E45" t="s">
-        <v>243</v>
-      </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>193</v>
-      </c>
-      <c r="B46" t="s">
-        <v>217</v>
-      </c>
-      <c r="D46" t="s">
-        <v>108</v>
-      </c>
-      <c r="E46" t="s">
-        <v>243</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>283</v>
-      </c>
-      <c r="B47" t="s">
-        <v>263</v>
-      </c>
-      <c r="C47" t="s">
-        <v>347</v>
-      </c>
-      <c r="D47" t="s">
-        <v>108</v>
-      </c>
-      <c r="E47" t="s">
-        <v>247</v>
-      </c>
-      <c r="F47" t="s">
-        <v>348</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>284</v>
-      </c>
-      <c r="B48" t="s">
-        <v>264</v>
-      </c>
-      <c r="D48" t="s">
-        <v>108</v>
-      </c>
-      <c r="E48" t="s">
-        <v>125</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="B49" t="s">
         <v>126</v>
       </c>
-      <c r="B49" t="s">
-        <v>127</v>
-      </c>
       <c r="C49" t="s">
+        <v>123</v>
+      </c>
+      <c r="D49" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" t="s">
         <v>124</v>
       </c>
-      <c r="D49" t="s">
-        <v>108</v>
-      </c>
-      <c r="E49" t="s">
-        <v>125</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>194</v>
+        <v>389</v>
       </c>
       <c r="B50" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C50" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E50" t="s">
-        <v>244</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E51" t="s">
-        <v>307</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s">
         <v>93</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>94</v>
       </c>
-      <c r="C52" t="s">
-        <v>95</v>
-      </c>
       <c r="D52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E52" t="s">
         <v>63</v>
       </c>
-      <c r="G52">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -2724,56 +2742,56 @@
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E53" t="s">
         <v>61</v>
       </c>
-      <c r="G53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C54" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E54" t="s">
-        <v>308</v>
-      </c>
-      <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>128</v>
+      </c>
+      <c r="B55" t="s">
         <v>129</v>
       </c>
-      <c r="B55" t="s">
-        <v>130</v>
-      </c>
       <c r="C55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E55" t="s">
-        <v>125</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -2781,244 +2799,244 @@
         <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E56" t="s">
         <v>62</v>
       </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>130</v>
+      </c>
+      <c r="B57" t="s">
         <v>131</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>132</v>
       </c>
-      <c r="C57" t="s">
-        <v>133</v>
-      </c>
       <c r="D57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E57" t="s">
-        <v>125</v>
-      </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B58" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D58" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E58" t="s">
         <v>77</v>
       </c>
-      <c r="G58">
+      <c r="J58">
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E59" t="s">
-        <v>125</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B60" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E60" t="s">
         <v>77</v>
       </c>
-      <c r="G60">
+      <c r="J60">
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>176</v>
+      </c>
+      <c r="B61" t="s">
         <v>177</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>337</v>
+      </c>
+      <c r="D61" t="s">
+        <v>140</v>
+      </c>
+      <c r="E61" t="s">
         <v>178</v>
       </c>
-      <c r="C61" t="s">
-        <v>340</v>
-      </c>
-      <c r="D61" t="s">
-        <v>141</v>
-      </c>
-      <c r="E61" t="s">
-        <v>179</v>
-      </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B62" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C62" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E62" t="s">
         <v>50</v>
       </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" t="s">
         <v>119</v>
       </c>
-      <c r="B63" t="s">
-        <v>120</v>
-      </c>
       <c r="D63" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E63" t="s">
         <v>63</v>
       </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B64" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C64" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D64" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B65" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C65" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D65" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E65" t="s">
-        <v>179</v>
-      </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D66" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E66" t="s">
-        <v>243</v>
-      </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B67" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C67" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E67" t="s">
-        <v>179</v>
-      </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>64</v>
       </c>
       <c r="B68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D68" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E68" t="s">
         <v>63</v>
       </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>74</v>
       </c>
@@ -3026,19 +3044,19 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D69" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E69" t="s">
         <v>49</v>
       </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -3046,7 +3064,7 @@
         <v>81</v>
       </c>
       <c r="D70" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E70" t="s">
         <v>77</v>
@@ -3054,142 +3072,142 @@
       <c r="F70" t="s">
         <v>82</v>
       </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D71" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E71" t="s">
-        <v>247</v>
-      </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="J71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E72" t="s">
-        <v>305</v>
-      </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+      <c r="J72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B73" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C73" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D73" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E73" t="s">
         <v>49</v>
       </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B74" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C74" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E74" t="s">
-        <v>243</v>
-      </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B75" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E75" t="s">
-        <v>179</v>
-      </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B76" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C76" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D76" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E76" t="s">
-        <v>179</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B77" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D77" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E77" t="s">
-        <v>137</v>
-      </c>
-      <c r="G77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -3197,39 +3215,39 @@
         <v>79</v>
       </c>
       <c r="C78" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E78" t="s">
         <v>77</v>
       </c>
-      <c r="G78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C79" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E79" t="s">
         <v>62</v>
       </c>
-      <c r="G79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="J79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>85</v>
       </c>
@@ -3237,247 +3255,247 @@
         <v>86</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D80" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E80" t="s">
         <v>62</v>
       </c>
-      <c r="G80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B81" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D81" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E81" t="s">
-        <v>308</v>
-      </c>
-      <c r="G81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B82" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C82" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D82" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E82" t="s">
-        <v>306</v>
-      </c>
-      <c r="G82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="J82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>113</v>
+      </c>
+      <c r="B83" t="s">
         <v>114</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>115</v>
       </c>
-      <c r="C83" t="s">
-        <v>116</v>
-      </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E83" t="s">
         <v>63</v>
       </c>
-      <c r="G83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B84" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C84" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D84" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E84" t="s">
         <v>77</v>
       </c>
-      <c r="G84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B85" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C85" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" t="s">
+        <v>140</v>
+      </c>
+      <c r="E85" t="s">
         <v>242</v>
       </c>
-      <c r="D85" t="s">
-        <v>141</v>
-      </c>
-      <c r="E85" t="s">
-        <v>245</v>
-      </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B86" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E86" t="s">
-        <v>179</v>
-      </c>
-      <c r="G86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B87" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C87" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D87" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E87" t="s">
         <v>77</v>
       </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B88" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C88" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D88" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E88" t="s">
-        <v>137</v>
-      </c>
-      <c r="G88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>90</v>
+      </c>
+      <c r="B89" t="s">
         <v>91</v>
       </c>
-      <c r="B89" t="s">
-        <v>92</v>
-      </c>
       <c r="C89" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D89" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E89" t="s">
         <v>63</v>
       </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B90" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E90" t="s">
-        <v>246</v>
-      </c>
-      <c r="G90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+        <v>243</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C91" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D91" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E91" t="s">
-        <v>179</v>
-      </c>
-      <c r="G91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" t="s">
         <v>112</v>
       </c>
-      <c r="B92" t="s">
-        <v>113</v>
-      </c>
       <c r="D92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E92" t="s">
-        <v>111</v>
-      </c>
-      <c r="G92">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>59</v>
       </c>
@@ -3485,190 +3503,190 @@
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D93" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E93" t="s">
         <v>49</v>
       </c>
-      <c r="G93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C94" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D94" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E94" t="s">
-        <v>179</v>
-      </c>
-      <c r="G94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B95" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C95" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
       </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B96" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D96" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E96" t="s">
-        <v>236</v>
-      </c>
-      <c r="G96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B97" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C97" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E97" t="s">
         <v>62</v>
       </c>
-      <c r="G97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
+        <v>292</v>
+      </c>
+      <c r="B98" t="s">
+        <v>270</v>
+      </c>
+      <c r="D98" t="s">
+        <v>107</v>
+      </c>
+      <c r="E98" t="s">
+        <v>303</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>201</v>
+      </c>
+      <c r="B99" t="s">
+        <v>225</v>
+      </c>
+      <c r="C99" t="s">
+        <v>328</v>
+      </c>
+      <c r="D99" t="s">
+        <v>140</v>
+      </c>
+      <c r="E99" t="s">
+        <v>235</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>306</v>
+      </c>
+      <c r="B100" t="s">
+        <v>271</v>
+      </c>
+      <c r="D100" t="s">
+        <v>107</v>
+      </c>
+      <c r="E100" t="s">
         <v>295</v>
       </c>
-      <c r="B98" t="s">
-        <v>273</v>
-      </c>
-      <c r="D98" t="s">
-        <v>108</v>
-      </c>
-      <c r="E98" t="s">
-        <v>306</v>
-      </c>
-      <c r="G98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
-        <v>203</v>
-      </c>
-      <c r="B99" t="s">
-        <v>228</v>
-      </c>
-      <c r="C99" t="s">
-        <v>331</v>
-      </c>
-      <c r="D99" t="s">
-        <v>141</v>
-      </c>
-      <c r="E99" t="s">
-        <v>238</v>
-      </c>
-      <c r="G99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>309</v>
-      </c>
-      <c r="B100" t="s">
-        <v>274</v>
-      </c>
-      <c r="D100" t="s">
-        <v>108</v>
-      </c>
-      <c r="E100" t="s">
-        <v>298</v>
-      </c>
-      <c r="G100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>204</v>
+        <v>390</v>
       </c>
       <c r="B101" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C101" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D101" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
       </c>
-      <c r="G101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>133</v>
+      </c>
+      <c r="B102" t="s">
         <v>134</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>135</v>
-      </c>
-      <c r="C102" t="s">
-        <v>136</v>
       </c>
       <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>137</v>
-      </c>
-      <c r="G102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>66</v>
       </c>
@@ -3676,36 +3694,36 @@
         <v>67</v>
       </c>
       <c r="C103" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E103" t="s">
         <v>63</v>
       </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="J103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B104" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E104" t="s">
-        <v>307</v>
-      </c>
-      <c r="G104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>53</v>
       </c>
@@ -3713,20 +3731,20 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D105" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E105" t="s">
         <v>50</v>
       </c>
-      <c r="G105">
+      <c r="J105">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G105" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
+  <autoFilter ref="A1:J105" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:F104">
     <sortCondition ref="B1:B104"/>
   </sortState>
@@ -3745,107 +3763,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3946,10 @@
         <v>88</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>385</v>
       </c>
       <c r="D5">
         <v>81260859</v>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59F74141-5EC8-D641-A54B-B4CE2A02778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA222A3-4257-394A-A550-DC7E67568CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10600" yWindow="1020" windowWidth="20120" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2420" yWindow="500" windowWidth="27300" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -213,9 +213,6 @@
     <t>Solberg</t>
   </si>
   <si>
-    <t>MrBot</t>
-  </si>
-  <si>
     <t>International Institute of Tropical Agriculture</t>
   </si>
   <si>
@@ -444,9 +441,6 @@
     <t>Hugo</t>
   </si>
   <si>
-    <t>Hugo Dorado-Betancourt</t>
-  </si>
-  <si>
     <t>0000-0002-0103-7505</t>
   </si>
   <si>
@@ -765,9 +759,6 @@
     <t>National Crop Resources Research Institute</t>
   </si>
   <si>
-    <t>Reputed Agriculture 4 Development Stichting &amp; Foundation</t>
-  </si>
-  <si>
     <t>Erna</t>
   </si>
   <si>
@@ -1185,9 +1176,6 @@
     <t>v0.9</t>
   </si>
   <si>
-    <t>Choose Grow Thrive: Using citizen science in expanding West Africa's food basket with African vegetables to tackle malnutrition (BMZ-CGT)”</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
@@ -1201,6 +1189,18 @@
   </si>
   <si>
     <t>Jacob</t>
+  </si>
+  <si>
+    <t>Choose Grow Thrive Using citizen science in expanding West Africa's food basket with African vegetables to tackle malnutrition (BMZ-CGT)”</t>
+  </si>
+  <si>
+    <t>Dorado-Betancourt</t>
+  </si>
+  <si>
+    <t>MrBot Software Solutions</t>
+  </si>
+  <si>
+    <t>Reputed Agriculture 4 Development Stichting and Foundation</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1630,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1638,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1646,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1686,7 +1686,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1694,7 +1694,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1702,7 +1702,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1719,7 +1719,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" customWidth="1"/>
@@ -1747,16 +1747,16 @@
         <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1804,16 +1804,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1821,16 +1821,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1838,16 +1838,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>245</v>
+        <v>390</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1855,16 +1855,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1872,19 +1872,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" t="s">
         <v>120</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>121</v>
       </c>
-      <c r="C8" t="s">
-        <v>122</v>
-      </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1892,19 +1892,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" t="s">
         <v>68</v>
       </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1912,19 +1912,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1932,16 +1932,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
         <v>50</v>
@@ -1952,16 +1952,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D12" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
@@ -1972,19 +1972,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E13" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1992,19 +1992,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" t="s">
         <v>310</v>
       </c>
-      <c r="C14" t="s">
-        <v>313</v>
-      </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2012,19 +2012,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2049,19 +2049,19 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C17" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2069,16 +2069,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2086,19 +2086,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D19" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2106,16 +2106,16 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>245</v>
+        <v>390</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2123,19 +2123,19 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2143,16 +2143,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B22" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C22" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D22" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E22" t="s">
         <v>50</v>
@@ -2163,16 +2163,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
         <v>116</v>
       </c>
-      <c r="B23" t="s">
-        <v>117</v>
-      </c>
       <c r="D23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2186,10 +2186,10 @@
         <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -2200,16 +2200,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B25" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D25" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2240,19 +2240,19 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C27" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2260,19 +2260,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
         <v>104</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2280,16 +2280,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" t="s">
         <v>108</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" t="s">
         <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" t="s">
-        <v>110</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2297,16 +2297,16 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B30" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B31" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D31" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E31" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C32" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D32" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -2351,19 +2351,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" t="s">
+        <v>138</v>
+      </c>
+      <c r="E33" t="s">
         <v>76</v>
-      </c>
-      <c r="C33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" t="s">
-        <v>140</v>
-      </c>
-      <c r="E33" t="s">
-        <v>77</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2371,16 +2371,16 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2388,16 +2388,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B35" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C35" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
@@ -2408,16 +2408,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2425,19 +2425,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C37" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2445,16 +2445,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B38" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E38" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2462,19 +2462,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C39" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2482,19 +2482,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
         <v>95</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>96</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
+        <v>106</v>
+      </c>
+      <c r="E40" t="s">
         <v>97</v>
-      </c>
-      <c r="D40" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" t="s">
-        <v>98</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2502,19 +2502,19 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
+        <v>136</v>
+      </c>
+      <c r="B41" t="s">
+        <v>388</v>
+      </c>
+      <c r="C41" t="s">
         <v>137</v>
       </c>
-      <c r="B41" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>139</v>
       </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
       <c r="E41" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F41" t="s">
         <v>50</v>
@@ -2525,19 +2525,19 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B42" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C42" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E42" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2545,19 +2545,19 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
+        <v>364</v>
+      </c>
+      <c r="B43" t="s">
+        <v>365</v>
+      </c>
+      <c r="C43" t="s">
+        <v>366</v>
+      </c>
+      <c r="D43" t="s">
+        <v>138</v>
+      </c>
+      <c r="E43" t="s">
         <v>367</v>
-      </c>
-      <c r="B43" t="s">
-        <v>368</v>
-      </c>
-      <c r="C43" t="s">
-        <v>369</v>
-      </c>
-      <c r="D43" t="s">
-        <v>140</v>
-      </c>
-      <c r="E43" t="s">
-        <v>370</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2565,16 +2565,16 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2582,19 +2582,19 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C45" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D45" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2602,16 +2602,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2619,22 +2619,22 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B47" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C47" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D47" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E47" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F47" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2642,16 +2642,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B48" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2659,19 +2659,19 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" t="s">
         <v>125</v>
       </c>
-      <c r="B49" t="s">
-        <v>126</v>
-      </c>
       <c r="C49" t="s">
+        <v>122</v>
+      </c>
+      <c r="D49" t="s">
+        <v>106</v>
+      </c>
+      <c r="E49" t="s">
         <v>123</v>
-      </c>
-      <c r="D49" t="s">
-        <v>107</v>
-      </c>
-      <c r="E49" t="s">
-        <v>124</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2679,19 +2679,19 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B50" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C50" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E50" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2699,16 +2699,16 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B51" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E51" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2716,19 +2716,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" t="s">
         <v>92</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>93</v>
       </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2742,10 +2742,10 @@
         <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E53" t="s">
-        <v>61</v>
+        <v>389</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2753,19 +2753,19 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C54" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E54" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2773,19 +2773,19 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
         <v>128</v>
       </c>
-      <c r="B55" t="s">
-        <v>129</v>
-      </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D55" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2799,13 +2799,13 @@
         <v>57</v>
       </c>
       <c r="C56" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2813,19 +2813,19 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" t="s">
         <v>130</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>131</v>
       </c>
-      <c r="C57" t="s">
-        <v>132</v>
-      </c>
       <c r="D57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2833,16 +2833,16 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D58" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -2850,16 +2850,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B59" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2867,16 +2867,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B60" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -2884,19 +2884,19 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" t="s">
+        <v>334</v>
+      </c>
+      <c r="D61" t="s">
+        <v>138</v>
+      </c>
+      <c r="E61" t="s">
         <v>176</v>
-      </c>
-      <c r="B61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C61" t="s">
-        <v>337</v>
-      </c>
-      <c r="D61" t="s">
-        <v>140</v>
-      </c>
-      <c r="E61" t="s">
-        <v>178</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -2904,16 +2904,16 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B62" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C62" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D62" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E62" t="s">
         <v>50</v>
@@ -2924,16 +2924,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" t="s">
         <v>118</v>
       </c>
-      <c r="B63" t="s">
-        <v>119</v>
-      </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2941,16 +2941,16 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B64" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C64" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D64" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
@@ -2961,19 +2961,19 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C65" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D65" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -2981,16 +2981,16 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E66" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -2998,19 +2998,19 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B67" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C67" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D67" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E67" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3018,19 +3018,19 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D68" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3038,16 +3038,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" t="s">
         <v>74</v>
       </c>
-      <c r="B69" t="s">
-        <v>75</v>
-      </c>
       <c r="C69" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E69" t="s">
         <v>49</v>
@@ -3058,19 +3058,19 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" t="s">
         <v>80</v>
       </c>
-      <c r="B70" t="s">
+      <c r="D70" t="s">
+        <v>168</v>
+      </c>
+      <c r="E70" t="s">
+        <v>76</v>
+      </c>
+      <c r="F70" t="s">
         <v>81</v>
-      </c>
-      <c r="D70" t="s">
-        <v>170</v>
-      </c>
-      <c r="E70" t="s">
-        <v>77</v>
-      </c>
-      <c r="F70" t="s">
-        <v>82</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3078,19 +3078,19 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C71" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D71" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E71" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3098,16 +3098,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B72" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E72" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3115,16 +3115,16 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B73" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C73" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D73" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E73" t="s">
         <v>49</v>
@@ -3135,19 +3135,19 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B74" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C74" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D74" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E74" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3155,16 +3155,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B75" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E75" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3172,19 +3172,19 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B76" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C76" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D76" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E76" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3192,16 +3192,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B77" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D77" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E77" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3209,19 +3209,19 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
         <v>78</v>
       </c>
-      <c r="B78" t="s">
-        <v>79</v>
-      </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D78" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E78" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3229,19 +3229,19 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C79" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D79" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -3249,19 +3249,19 @@
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80" t="s">
         <v>85</v>
       </c>
-      <c r="B80" t="s">
-        <v>86</v>
-      </c>
       <c r="C80" s="6" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E80" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3269,16 +3269,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D81" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E81" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -3286,19 +3286,19 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B82" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C82" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D82" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E82" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -3306,19 +3306,19 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
+        <v>112</v>
+      </c>
+      <c r="B83" t="s">
         <v>113</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>114</v>
       </c>
-      <c r="C83" t="s">
-        <v>115</v>
-      </c>
       <c r="D83" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -3326,19 +3326,19 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B84" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C84" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D84" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E84" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -3346,19 +3346,19 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C85" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D85" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E85" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -3366,16 +3366,16 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D86" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -3383,19 +3383,19 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B87" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C87" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E87" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J87">
         <v>1</v>
@@ -3403,19 +3403,19 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B88" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C88" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D88" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E88" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -3423,19 +3423,19 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>89</v>
+      </c>
+      <c r="B89" t="s">
         <v>90</v>
       </c>
-      <c r="B89" t="s">
-        <v>91</v>
-      </c>
       <c r="C89" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -3443,16 +3443,16 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D90" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3460,19 +3460,19 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B91" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C91" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D91" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E91" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -3480,16 +3480,16 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
+        <v>110</v>
+      </c>
+      <c r="B92" t="s">
         <v>111</v>
       </c>
-      <c r="B92" t="s">
-        <v>112</v>
-      </c>
       <c r="D92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -3503,10 +3503,10 @@
         <v>60</v>
       </c>
       <c r="C93" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D93" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E93" t="s">
         <v>49</v>
@@ -3517,19 +3517,19 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B94" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C94" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E94" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -3537,16 +3537,16 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B95" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C95" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D95" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
@@ -3557,16 +3557,16 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B96" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D96" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E96" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -3574,19 +3574,19 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C97" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D97" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -3594,16 +3594,16 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B98" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E98" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -3611,19 +3611,19 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B99" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C99" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D99" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E99" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3631,16 +3631,16 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B100" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D100" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E100" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3648,16 +3648,16 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B101" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C101" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D101" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
@@ -3668,19 +3668,19 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
+        <v>132</v>
+      </c>
+      <c r="B102" t="s">
         <v>133</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>134</v>
-      </c>
-      <c r="C102" t="s">
-        <v>135</v>
       </c>
       <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3688,19 +3688,19 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>65</v>
+      </c>
+      <c r="B103" t="s">
         <v>66</v>
       </c>
-      <c r="B103" t="s">
-        <v>67</v>
-      </c>
       <c r="C103" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E103" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J103">
         <v>1</v>
@@ -3708,16 +3708,16 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B104" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D104" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E104" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3731,10 +3731,10 @@
         <v>54</v>
       </c>
       <c r="C105" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D105" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E105" t="s">
         <v>50</v>
@@ -3763,107 +3763,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3935,21 +3935,21 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
         <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>81260859</v>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA222A3-4257-394A-A550-DC7E67568CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACEFBF4-22E0-7945-883D-EDB6FDA32F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="500" windowWidth="27300" windowHeight="16680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2420" yWindow="500" windowWidth="27300" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -1167,15 +1167,9 @@
     <t>0000-0001-6887-4095</t>
   </si>
   <si>
-    <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. ‘Triadic’ refers to the sets of three technology options that are compared by each participant. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
-  </si>
-  <si>
     <t>2025-09-10</t>
   </si>
   <si>
-    <t>v0.9</t>
-  </si>
-  <si>
     <t>email</t>
   </si>
   <si>
@@ -1201,6 +1195,12 @@
   </si>
   <si>
     <t>Reputed Agriculture 4 Development Stichting and Foundation</t>
+  </si>
+  <si>
+    <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
+  </si>
+  <si>
+    <t>v0.1</t>
   </si>
 </sst>
 </file>
@@ -1638,7 +1638,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1646,7 +1646,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1657,12 +1657,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="144" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="128" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1747,13 +1747,13 @@
         <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>382</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>384</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>305</v>
@@ -1847,7 +1847,7 @@
         <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2115,7 +2115,7 @@
         <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2505,7 +2505,7 @@
         <v>136</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C41" t="s">
         <v>137</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B50" t="s">
         <v>213</v>
@@ -2745,7 +2745,7 @@
         <v>106</v>
       </c>
       <c r="E53" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -3648,7 +3648,7 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B101" t="s">
         <v>224</v>
@@ -3949,7 +3949,7 @@
         <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D5">
         <v>81260859</v>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACEFBF4-22E0-7945-883D-EDB6FDA32F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7057BE28-4DC7-784E-B6C9-CE41137794DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2420" yWindow="500" windowWidth="27300" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="390">
   <si>
     <t>key</t>
   </si>
@@ -189,9 +189,6 @@
     <t>Cremaschi</t>
   </si>
   <si>
-    <t xml:space="preserve">Jacob </t>
-  </si>
-  <si>
     <t>van Etten</t>
   </si>
   <si>
@@ -231,9 +228,6 @@
     <t>van Zonneveld</t>
   </si>
   <si>
-    <t xml:space="preserve">Lys Amavi </t>
-  </si>
-  <si>
     <t>Aglinglo</t>
   </si>
   <si>
@@ -267,9 +261,6 @@
     <t>Ojiewo</t>
   </si>
   <si>
-    <t xml:space="preserve">Ganga Rao V. P. R. </t>
-  </si>
-  <si>
     <t>Nadigatla</t>
   </si>
   <si>
@@ -303,18 +294,12 @@
     <t>Shango</t>
   </si>
   <si>
-    <t xml:space="preserve">Eric C. </t>
-  </si>
-  <si>
     <t>Legba</t>
   </si>
   <si>
     <t>0009-0008-8284-0463</t>
   </si>
   <si>
-    <t xml:space="preserve">Aristide Carlos </t>
-  </si>
-  <si>
     <t>Houdegbe</t>
   </si>
   <si>
@@ -339,9 +324,6 @@
     <t>0009-0005-1515-4699</t>
   </si>
   <si>
-    <t xml:space="preserve">Danfing dit Youssouf </t>
-  </si>
-  <si>
     <t>Diarra</t>
   </si>
   <si>
@@ -351,18 +333,12 @@
     <t>dataproducer</t>
   </si>
   <si>
-    <t xml:space="preserve">Aminata </t>
-  </si>
-  <si>
     <t>Dolo</t>
   </si>
   <si>
     <t>Institut d'Economie Rurale</t>
   </si>
   <si>
-    <t xml:space="preserve">Amadou </t>
-  </si>
-  <si>
     <t>Sidibe</t>
   </si>
   <si>
@@ -375,9 +351,6 @@
     <t>0000-0002-1997-3684</t>
   </si>
   <si>
-    <t xml:space="preserve">Harouna </t>
-  </si>
-  <si>
     <t>Coulibaly</t>
   </si>
   <si>
@@ -387,9 +360,6 @@
     <t>Mlaki</t>
   </si>
   <si>
-    <t xml:space="preserve">Enoch G. </t>
-  </si>
-  <si>
     <t>Achigan-Dako</t>
   </si>
   <si>
@@ -402,18 +372,12 @@
     <t>Tanzania Agricultural Research Institute</t>
   </si>
   <si>
-    <t xml:space="preserve">Aishi </t>
-  </si>
-  <si>
     <t>Kileo</t>
   </si>
   <si>
     <t>0009-0005-5327-6769</t>
   </si>
   <si>
-    <t xml:space="preserve">Dickson </t>
-  </si>
-  <si>
     <t>Malulu</t>
   </si>
   <si>
@@ -426,9 +390,6 @@
     <t>0009-0005-4091-782X</t>
   </si>
   <si>
-    <t xml:space="preserve">Joost </t>
-  </si>
-  <si>
     <t>van Heerwaarden</t>
   </si>
   <si>
@@ -540,9 +501,6 @@
     <t>Global multi-crop agricultural trial data supported by citizen science</t>
   </si>
   <si>
-    <t>participatory variety testing; digital innovation; tricot approach; FAIR data</t>
-  </si>
-  <si>
     <t>cc-by-sa-4.0</t>
   </si>
   <si>
@@ -753,9 +711,6 @@
     <t>Zamorano University</t>
   </si>
   <si>
-    <t>Tuberosum Technologies Inc.</t>
-  </si>
-  <si>
     <t>National Crop Resources Research Institute</t>
   </si>
   <si>
@@ -765,9 +720,6 @@
     <t>Abidin</t>
   </si>
   <si>
-    <t xml:space="preserve">Bello </t>
-  </si>
-  <si>
     <t>Abolore</t>
   </si>
   <si>
@@ -777,9 +729,6 @@
     <t>Dawud</t>
   </si>
   <si>
-    <t xml:space="preserve">Gospel </t>
-  </si>
-  <si>
     <t>Edughaen</t>
   </si>
   <si>
@@ -849,63 +798,9 @@
     <t>Yeye</t>
   </si>
   <si>
-    <t xml:space="preserve">Sanusi </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvin </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Edith </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teshale M. </t>
-  </si>
-  <si>
     <t>Robert</t>
   </si>
   <si>
-    <t xml:space="preserve">Michael </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julius </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mukani </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olamide </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Richard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Placide </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pieter </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muhammad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samuel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tessy Ugo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theophilus Kwabla </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Athanase </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jean Claude </t>
-  </si>
-  <si>
     <t>One Acre Fund</t>
   </si>
   <si>
@@ -1200,7 +1095,109 @@
     <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
   </si>
   <si>
-    <t>v0.1</t>
+    <t>v0.2</t>
+  </si>
+  <si>
+    <t>agriculture; digital innovation; FAIR data; partnerships for the goals; tricot approach;</t>
+  </si>
+  <si>
+    <t>Bello</t>
+  </si>
+  <si>
+    <t>Harouna</t>
+  </si>
+  <si>
+    <t>Aminata</t>
+  </si>
+  <si>
+    <t>Gospel</t>
+  </si>
+  <si>
+    <t>Sanusi</t>
+  </si>
+  <si>
+    <t>Marvin</t>
+  </si>
+  <si>
+    <t>Edith</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Aishi</t>
+  </si>
+  <si>
+    <t>Muhammad</t>
+  </si>
+  <si>
+    <t>Dickson</t>
+  </si>
+  <si>
+    <t>Julius</t>
+  </si>
+  <si>
+    <t>Mukani</t>
+  </si>
+  <si>
+    <t>Athanase</t>
+  </si>
+  <si>
+    <t>Olamide</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Placide</t>
+  </si>
+  <si>
+    <t>Pieter</t>
+  </si>
+  <si>
+    <t>Amadou</t>
+  </si>
+  <si>
+    <t>Joost</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Enoch G.</t>
+  </si>
+  <si>
+    <t>Lys Amavi</t>
+  </si>
+  <si>
+    <t>Teshale M.</t>
+  </si>
+  <si>
+    <t>Danfing dit Youssouf</t>
+  </si>
+  <si>
+    <t>Aristide Carlos</t>
+  </si>
+  <si>
+    <t>Eric C.</t>
+  </si>
+  <si>
+    <t>Tessy Ugo</t>
+  </si>
+  <si>
+    <t>Ganga Rao V. P. R.</t>
+  </si>
+  <si>
+    <t>Jean Claude</t>
+  </si>
+  <si>
+    <t>Tuberosum Technologies Inc</t>
+  </si>
+  <si>
+    <t>Theophilus Kwabla</t>
   </si>
 </sst>
 </file>
@@ -1614,7 +1611,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="2" max="2" width="67.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -1630,7 +1627,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1638,7 +1635,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>390</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1646,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>379</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1662,7 +1659,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>389</v>
+        <v>354</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1686,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1694,7 +1691,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1702,7 +1699,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -1722,7 +1719,7 @@
     <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.33203125" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
     <col min="6" max="9" width="13.5" customWidth="1"/>
     <col min="10" max="10" width="14.1640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1747,16 +1744,16 @@
         <v>21</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>380</v>
+        <v>345</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -1804,16 +1801,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>348</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>349</v>
+        <v>314</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1821,16 +1818,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>293</v>
+        <v>258</v>
       </c>
       <c r="B5" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1838,16 +1835,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1855,16 +1852,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>357</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1872,19 +1869,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>379</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1892,19 +1889,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>67</v>
+        <v>380</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1912,19 +1909,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
-        <v>320</v>
+        <v>285</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1932,16 +1929,16 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B11" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C11" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
         <v>50</v>
@@ -1952,16 +1949,16 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="B12" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>316</v>
+        <v>281</v>
       </c>
       <c r="D12" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E12" t="s">
         <v>50</v>
@@ -1972,19 +1969,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1992,19 +1989,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>272</v>
       </c>
       <c r="C14" t="s">
-        <v>310</v>
+        <v>275</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2012,19 +2009,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>318</v>
+        <v>283</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2032,16 +2029,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="D16" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2049,19 +2046,19 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C17" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2069,16 +2066,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2086,19 +2083,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C19" t="s">
-        <v>317</v>
+        <v>282</v>
       </c>
       <c r="D19" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E19" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2106,16 +2103,16 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B20" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>388</v>
+        <v>353</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2123,19 +2120,19 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="B21" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="C21" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2143,16 +2140,16 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="D22" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E22" t="s">
         <v>50</v>
@@ -2163,16 +2160,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>358</v>
       </c>
       <c r="B23" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2186,10 +2183,10 @@
         <v>52</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
         <v>50</v>
@@ -2200,16 +2197,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>373</v>
+        <v>338</v>
       </c>
       <c r="B25" t="s">
-        <v>374</v>
+        <v>339</v>
       </c>
       <c r="D25" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="E25" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2217,22 +2214,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="D26" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2240,19 +2237,19 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="C27" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>296</v>
+        <v>261</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2260,19 +2257,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>382</v>
       </c>
       <c r="B28" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="D28" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2280,16 +2277,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>359</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2297,16 +2294,16 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>249</v>
+        <v>360</v>
       </c>
       <c r="B30" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2314,16 +2311,16 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B31" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E31" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2331,16 +2328,16 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E32" t="s">
         <v>50</v>
@@ -2351,19 +2348,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="D33" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2371,16 +2368,16 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>273</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2388,16 +2385,16 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E35" t="s">
         <v>50</v>
@@ -2408,16 +2405,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>274</v>
+        <v>362</v>
       </c>
       <c r="B36" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E36" t="s">
-        <v>298</v>
+        <v>263</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2425,19 +2422,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="C37" t="s">
-        <v>333</v>
+        <v>298</v>
       </c>
       <c r="D37" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2445,16 +2442,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>351</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
-        <v>352</v>
+        <v>317</v>
       </c>
       <c r="D38" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E38" t="s">
-        <v>350</v>
+        <v>315</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2462,19 +2459,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>236</v>
+        <v>222</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2482,19 +2479,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2502,19 +2499,19 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="B41" t="s">
-        <v>386</v>
+        <v>351</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="D41" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="F41" t="s">
         <v>50</v>
@@ -2525,19 +2522,19 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>214</v>
+      </c>
+      <c r="C42" t="s">
+        <v>304</v>
+      </c>
+      <c r="D42" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" t="s">
         <v>227</v>
-      </c>
-      <c r="B42" t="s">
-        <v>228</v>
-      </c>
-      <c r="C42" t="s">
-        <v>339</v>
-      </c>
-      <c r="D42" t="s">
-        <v>106</v>
-      </c>
-      <c r="E42" t="s">
-        <v>242</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2545,19 +2542,19 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>364</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s">
-        <v>365</v>
+        <v>330</v>
       </c>
       <c r="C43" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>367</v>
+        <v>332</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2565,16 +2562,16 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>275</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="D44" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E44" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2582,19 +2579,19 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="C45" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E45" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2602,16 +2599,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="D46" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E46" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2619,22 +2616,22 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="B47" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="C47" t="s">
-        <v>341</v>
+        <v>306</v>
       </c>
       <c r="D47" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F47" t="s">
-        <v>342</v>
+        <v>307</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2642,16 +2639,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2659,19 +2656,19 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D49" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2679,19 +2676,19 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="C50" t="s">
-        <v>357</v>
+        <v>322</v>
       </c>
       <c r="D50" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2699,16 +2696,16 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E51" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2716,19 +2713,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>91</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2736,16 +2733,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D53" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E53" t="s">
-        <v>387</v>
+        <v>352</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2753,19 +2750,19 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="C54" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="D54" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E54" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2773,19 +2770,19 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>127</v>
+        <v>367</v>
       </c>
       <c r="B55" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E55" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2793,19 +2790,19 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="D56" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2813,19 +2810,19 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B57" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E57" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2833,16 +2830,16 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="B58" t="s">
-        <v>354</v>
+        <v>319</v>
       </c>
       <c r="D58" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E58" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J58">
         <v>0</v>
@@ -2850,16 +2847,16 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>279</v>
+        <v>368</v>
       </c>
       <c r="B59" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="D59" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E59" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2867,16 +2864,16 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="B60" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
       <c r="D60" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E60" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -2884,19 +2881,19 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="B61" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="C61" t="s">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E61" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -2904,16 +2901,16 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B62" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C62" t="s">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="D62" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E62" t="s">
         <v>50</v>
@@ -2924,16 +2921,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D63" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E63" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2941,16 +2938,16 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>370</v>
+        <v>335</v>
       </c>
       <c r="B64" t="s">
-        <v>371</v>
+        <v>336</v>
       </c>
       <c r="C64" t="s">
-        <v>372</v>
+        <v>337</v>
       </c>
       <c r="D64" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E64" t="s">
         <v>49</v>
@@ -2961,19 +2958,19 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>280</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C65" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="D65" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E65" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -2981,16 +2978,16 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>369</v>
+        <v>334</v>
       </c>
       <c r="B66" t="s">
-        <v>368</v>
+        <v>333</v>
       </c>
       <c r="D66" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E66" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -2998,19 +2995,19 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="B67" t="s">
-        <v>308</v>
+        <v>273</v>
       </c>
       <c r="C67" t="s">
-        <v>309</v>
+        <v>274</v>
       </c>
       <c r="D67" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E67" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3018,19 +3015,19 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D68" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3038,16 +3035,16 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C69" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="D69" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E69" t="s">
         <v>49</v>
@@ -3058,19 +3055,19 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>386</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D70" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="E70" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F70" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3078,19 +3075,19 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="B71" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C71" t="s">
-        <v>338</v>
+        <v>303</v>
       </c>
       <c r="D71" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E71" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3098,16 +3095,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="B72" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="D72" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3115,16 +3112,16 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="B73" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="C73" t="s">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="D73" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E73" t="s">
         <v>49</v>
@@ -3135,19 +3132,19 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>361</v>
+        <v>326</v>
       </c>
       <c r="B74" t="s">
-        <v>362</v>
+        <v>327</v>
       </c>
       <c r="C74" t="s">
-        <v>363</v>
+        <v>328</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E74" t="s">
-        <v>238</v>
+        <v>224</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3155,16 +3152,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>291</v>
+        <v>387</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E75" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3172,19 +3169,19 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>311</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="C76" t="s">
-        <v>313</v>
+        <v>278</v>
       </c>
       <c r="D76" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E76" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3192,16 +3189,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="B77" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D77" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E77" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3209,19 +3206,19 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C78" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E78" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3229,19 +3226,19 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>281</v>
+        <v>371</v>
       </c>
       <c r="B79" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="C79" t="s">
-        <v>321</v>
+        <v>286</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E79" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -3249,19 +3246,19 @@
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B80" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="D80" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E80" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3269,16 +3266,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>286</v>
+        <v>372</v>
       </c>
       <c r="B81" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="D81" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E81" t="s">
-        <v>302</v>
+        <v>267</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -3286,19 +3283,19 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>282</v>
+        <v>373</v>
       </c>
       <c r="B82" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="C82" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="D82" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E82" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -3306,19 +3303,19 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E83" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -3326,19 +3323,19 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="B84" t="s">
-        <v>377</v>
+        <v>342</v>
       </c>
       <c r="C84" t="s">
-        <v>378</v>
+        <v>343</v>
       </c>
       <c r="D84" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="E84" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -3346,19 +3343,19 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B85" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
       <c r="C85" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E85" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -3366,16 +3363,16 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>283</v>
+        <v>374</v>
       </c>
       <c r="B86" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="D86" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E86" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -3383,19 +3380,19 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>375</v>
       </c>
       <c r="B87" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C87" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="D87" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E87" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J87">
         <v>1</v>
@@ -3403,19 +3400,19 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C88" t="s">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="D88" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="E88" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -3423,19 +3420,19 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C89" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D89" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E89" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -3443,16 +3440,16 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="D90" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E90" t="s">
-        <v>241</v>
+        <v>388</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3460,19 +3457,19 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="B91" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>322</v>
+        <v>287</v>
       </c>
       <c r="D91" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E91" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -3480,16 +3477,16 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>110</v>
+        <v>376</v>
       </c>
       <c r="B92" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D92" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E92" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -3497,16 +3494,16 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
+        <v>58</v>
+      </c>
+      <c r="B93" t="s">
         <v>59</v>
       </c>
-      <c r="B93" t="s">
-        <v>60</v>
-      </c>
       <c r="C93" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D93" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E93" t="s">
         <v>49</v>
@@ -3517,19 +3514,19 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="B94" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C94" t="s">
-        <v>346</v>
+        <v>311</v>
       </c>
       <c r="D94" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E94" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -3537,16 +3534,16 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="B95" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="C95" t="s">
-        <v>323</v>
+        <v>288</v>
       </c>
       <c r="D95" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E95" t="s">
         <v>50</v>
@@ -3557,16 +3554,16 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B96" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="D96" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E96" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -3574,19 +3571,19 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B97" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="C97" t="s">
-        <v>324</v>
+        <v>289</v>
       </c>
       <c r="D97" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E97" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -3594,16 +3591,16 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>289</v>
+        <v>389</v>
       </c>
       <c r="B98" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="D98" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E98" t="s">
-        <v>300</v>
+        <v>265</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -3611,19 +3608,19 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C99" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E99" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3631,16 +3628,16 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>303</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="D100" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E100" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3648,16 +3645,16 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="B101" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="C101" t="s">
-        <v>347</v>
+        <v>312</v>
       </c>
       <c r="D101" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E101" t="s">
         <v>50</v>
@@ -3668,19 +3665,19 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>132</v>
+        <v>377</v>
       </c>
       <c r="B102" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C102" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="D102" t="s">
         <v>28</v>
       </c>
       <c r="E102" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3688,19 +3685,19 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" t="s">
         <v>65</v>
       </c>
-      <c r="B103" t="s">
-        <v>66</v>
-      </c>
       <c r="C103" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E103" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J103">
         <v>1</v>
@@ -3708,16 +3705,16 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>288</v>
+        <v>378</v>
       </c>
       <c r="B104" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="D104" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E104" t="s">
-        <v>301</v>
+        <v>266</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3725,16 +3722,16 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
+        <v>349</v>
+      </c>
+      <c r="B105" t="s">
         <v>53</v>
       </c>
-      <c r="B105" t="s">
-        <v>54</v>
-      </c>
       <c r="C105" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="D105" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E105" t="s">
         <v>50</v>
@@ -3763,107 +3760,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -3935,21 +3932,21 @@
         <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>350</v>
       </c>
       <c r="D5">
         <v>81260859</v>

--- a/metadata/project-metadata.xlsx
+++ b/metadata/project-metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/tricot-data/metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kauedesousa/Library/Mobile Documents/com~apple~CloudDocs/Work/Rcode/test-data-tricot/metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7057BE28-4DC7-784E-B6C9-CE41137794DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB3C2E3-7CE2-404B-BE66-1E6B6A3B9CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30720" windowHeight="16580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="roles_options" sheetId="6" r:id="rId3"/>
     <sheet name="funders" sheetId="3" r:id="rId4"/>
     <sheet name="communities" sheetId="4" r:id="rId5"/>
-    <sheet name="dates" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">authors!$A$1:$J$105</definedName>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="385">
   <si>
     <t>key</t>
   </si>
@@ -66,9 +65,6 @@
     <t>subjects</t>
   </si>
   <si>
-    <t>2025-04-14</t>
-  </si>
-  <si>
     <t>Zenodo</t>
   </si>
   <si>
@@ -138,18 +134,6 @@
     <t>community_name</t>
   </si>
   <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>accepted</t>
-  </si>
-  <si>
-    <t>submitted</t>
-  </si>
-  <si>
     <t>https://ror.org/04zbn7k04</t>
   </si>
   <si>
@@ -1092,112 +1076,112 @@
     <t>Reputed Agriculture 4 Development Stichting and Foundation</t>
   </si>
   <si>
+    <t>Bello</t>
+  </si>
+  <si>
+    <t>Harouna</t>
+  </si>
+  <si>
+    <t>Aminata</t>
+  </si>
+  <si>
+    <t>Gospel</t>
+  </si>
+  <si>
+    <t>Sanusi</t>
+  </si>
+  <si>
+    <t>Marvin</t>
+  </si>
+  <si>
+    <t>Edith</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Aishi</t>
+  </si>
+  <si>
+    <t>Muhammad</t>
+  </si>
+  <si>
+    <t>Dickson</t>
+  </si>
+  <si>
+    <t>Julius</t>
+  </si>
+  <si>
+    <t>Mukani</t>
+  </si>
+  <si>
+    <t>Athanase</t>
+  </si>
+  <si>
+    <t>Olamide</t>
+  </si>
+  <si>
+    <t>Samuel</t>
+  </si>
+  <si>
+    <t>Richard</t>
+  </si>
+  <si>
+    <t>Placide</t>
+  </si>
+  <si>
+    <t>Pieter</t>
+  </si>
+  <si>
+    <t>Amadou</t>
+  </si>
+  <si>
+    <t>Joost</t>
+  </si>
+  <si>
+    <t>Mary</t>
+  </si>
+  <si>
+    <t>Enoch G.</t>
+  </si>
+  <si>
+    <t>Lys Amavi</t>
+  </si>
+  <si>
+    <t>Teshale M.</t>
+  </si>
+  <si>
+    <t>Danfing dit Youssouf</t>
+  </si>
+  <si>
+    <t>Aristide Carlos</t>
+  </si>
+  <si>
+    <t>Eric C.</t>
+  </si>
+  <si>
+    <t>Tessy Ugo</t>
+  </si>
+  <si>
+    <t>Ganga Rao V. P. R.</t>
+  </si>
+  <si>
+    <t>Jean Claude</t>
+  </si>
+  <si>
+    <t>Tuberosum Technologies Inc</t>
+  </si>
+  <si>
+    <t>Theophilus Kwabla</t>
+  </si>
+  <si>
+    <t>v0.4</t>
+  </si>
+  <si>
+    <t>agriculture; digital innovation; FAIR data; partnerships for the goals; tricot approach</t>
+  </si>
+  <si>
     <t>The triadic comparison of technologies (tricot) is a citizen science approach for testing technology options in their target environments, which has been applied to on-farm testing of crop varieties. In the approach, participants are invited to test a anonymous set of three technologies (out of a larger number, generally between 5 to 20) randomly assigned. Between 2011 and 2025 the tricot approach was applied in more than 25 countries across Africa, Asia, Europe and Latin America with more than 30 crops.</t>
-  </si>
-  <si>
-    <t>v0.2</t>
-  </si>
-  <si>
-    <t>agriculture; digital innovation; FAIR data; partnerships for the goals; tricot approach;</t>
-  </si>
-  <si>
-    <t>Bello</t>
-  </si>
-  <si>
-    <t>Harouna</t>
-  </si>
-  <si>
-    <t>Aminata</t>
-  </si>
-  <si>
-    <t>Gospel</t>
-  </si>
-  <si>
-    <t>Sanusi</t>
-  </si>
-  <si>
-    <t>Marvin</t>
-  </si>
-  <si>
-    <t>Edith</t>
-  </si>
-  <si>
-    <t>Michael</t>
-  </si>
-  <si>
-    <t>Aishi</t>
-  </si>
-  <si>
-    <t>Muhammad</t>
-  </si>
-  <si>
-    <t>Dickson</t>
-  </si>
-  <si>
-    <t>Julius</t>
-  </si>
-  <si>
-    <t>Mukani</t>
-  </si>
-  <si>
-    <t>Athanase</t>
-  </si>
-  <si>
-    <t>Olamide</t>
-  </si>
-  <si>
-    <t>Samuel</t>
-  </si>
-  <si>
-    <t>Richard</t>
-  </si>
-  <si>
-    <t>Placide</t>
-  </si>
-  <si>
-    <t>Pieter</t>
-  </si>
-  <si>
-    <t>Amadou</t>
-  </si>
-  <si>
-    <t>Joost</t>
-  </si>
-  <si>
-    <t>Mary</t>
-  </si>
-  <si>
-    <t>Enoch G.</t>
-  </si>
-  <si>
-    <t>Lys Amavi</t>
-  </si>
-  <si>
-    <t>Teshale M.</t>
-  </si>
-  <si>
-    <t>Danfing dit Youssouf</t>
-  </si>
-  <si>
-    <t>Aristide Carlos</t>
-  </si>
-  <si>
-    <t>Eric C.</t>
-  </si>
-  <si>
-    <t>Tessy Ugo</t>
-  </si>
-  <si>
-    <t>Ganga Rao V. P. R.</t>
-  </si>
-  <si>
-    <t>Jean Claude</t>
-  </si>
-  <si>
-    <t>Tuberosum Technologies Inc</t>
-  </si>
-  <si>
-    <t>Theophilus Kwabla</t>
   </si>
 </sst>
 </file>
@@ -1627,7 +1611,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -1635,7 +1619,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -1643,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1651,15 +1635,15 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="128" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="96" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>354</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -1667,7 +1651,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -1675,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -1683,7 +1667,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -1691,7 +1675,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
@@ -1699,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -1726,54 +1710,54 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -1781,19 +1765,19 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>28</v>
-      </c>
       <c r="E3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1801,16 +1785,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1818,16 +1802,16 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1835,16 +1819,16 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B6" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -1852,16 +1836,16 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="B7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -1869,19 +1853,19 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -1889,19 +1873,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -1909,19 +1893,19 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -1929,19 +1913,19 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C11" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -1949,19 +1933,19 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D12" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E12" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -1969,19 +1953,19 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B13" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="C13" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D13" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -1989,19 +1973,19 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B14" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2009,19 +1993,19 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -2029,16 +2013,16 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D16" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2046,19 +2030,19 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J17">
         <v>1</v>
@@ -2066,16 +2050,16 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J18">
         <v>1</v>
@@ -2083,19 +2067,19 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C19" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D19" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E19" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -2103,16 +2087,16 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E20" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="J20">
         <v>1</v>
@@ -2120,19 +2104,19 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C21" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J21">
         <v>1</v>
@@ -2140,19 +2124,19 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B22" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C22" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D22" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E22" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J22">
         <v>1</v>
@@ -2160,16 +2144,16 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -2177,19 +2161,19 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -2197,16 +2181,16 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B25" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D25" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E25" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J25">
         <v>1</v>
@@ -2214,22 +2198,22 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J26">
         <v>1</v>
@@ -2237,19 +2221,19 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C27" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D27" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E27" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J27">
         <v>1</v>
@@ -2257,19 +2241,19 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -2277,16 +2261,16 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="B29" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E29" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2294,16 +2278,16 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B30" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J30">
         <v>1</v>
@@ -2311,16 +2295,16 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B31" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D31" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J31">
         <v>1</v>
@@ -2328,19 +2312,19 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J32">
         <v>1</v>
@@ -2348,19 +2332,19 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J33">
         <v>1</v>
@@ -2368,16 +2352,16 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E34" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2385,19 +2369,19 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C35" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D35" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -2405,16 +2389,16 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D36" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E36" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="J36">
         <v>1</v>
@@ -2422,19 +2406,19 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C37" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D37" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E37" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J37">
         <v>1</v>
@@ -2442,16 +2426,16 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E38" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="J38">
         <v>1</v>
@@ -2459,19 +2443,19 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C39" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E39" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2479,19 +2463,19 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C40" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D40" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E40" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="J40">
         <v>1</v>
@@ -2499,22 +2483,22 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C41" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E41" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2522,19 +2506,19 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C42" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D42" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E42" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J42">
         <v>1</v>
@@ -2542,19 +2526,19 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="C43" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="J43">
         <v>1</v>
@@ -2562,16 +2546,16 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D44" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E44" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2579,19 +2563,19 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C45" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E45" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J45">
         <v>1</v>
@@ -2599,16 +2583,16 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D46" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J46">
         <v>1</v>
@@ -2616,22 +2600,22 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B47" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="C47" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E47" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F47" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="J47">
         <v>1</v>
@@ -2639,16 +2623,16 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B48" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E48" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J48">
         <v>1</v>
@@ -2656,19 +2640,19 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E49" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -2676,19 +2660,19 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C50" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E50" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2696,16 +2680,16 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D51" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E51" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J51">
         <v>1</v>
@@ -2713,19 +2697,19 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E52" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2733,16 +2717,16 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D53" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E53" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="J53">
         <v>1</v>
@@ -2750,19 +2734,19 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C54" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D54" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E54" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -2770,19 +2754,19 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C55" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D55" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J55">
         <v>1</v>
@@ -2790,19 +2774,19 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C56" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E56" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J56">
         <v>1</v>
@@ -2810,19 +2794,19 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E57" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J57">
         <v>1</v>
@@ -2830,33 +2814,33 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B58" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="D58" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E58" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B59" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D59" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E59" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -2864,36 +2848,36 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="B60" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="D60" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E60" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C61" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D61" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E61" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J61">
         <v>1</v>
@@ -2901,19 +2885,19 @@
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B62" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C62" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E62" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J62">
         <v>1</v>
@@ -2921,16 +2905,16 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D63" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E63" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J63">
         <v>1</v>
@@ -2938,19 +2922,19 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B64" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C64" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D64" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E64" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -2958,19 +2942,19 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B65" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C65" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E65" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J65">
         <v>1</v>
@@ -2978,16 +2962,16 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B66" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="D66" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E66" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -2995,19 +2979,19 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B67" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="C67" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D67" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E67" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J67">
         <v>1</v>
@@ -3015,19 +2999,19 @@
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C68" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E68" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J68">
         <v>1</v>
@@ -3035,19 +3019,19 @@
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C69" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E69" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -3055,19 +3039,19 @@
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="B70" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D70" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E70" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F70" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J70">
         <v>1</v>
@@ -3075,19 +3059,19 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B71" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C71" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E71" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -3095,16 +3079,16 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B72" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E72" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J72">
         <v>1</v>
@@ -3112,19 +3096,19 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B73" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C73" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="D73" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E73" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J73">
         <v>1</v>
@@ -3132,19 +3116,19 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="C74" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D74" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E74" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -3152,16 +3136,16 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B75" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D75" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E75" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J75">
         <v>1</v>
@@ -3169,19 +3153,19 @@
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B76" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="C76" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D76" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E76" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J76">
         <v>1</v>
@@ -3189,16 +3173,16 @@
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D77" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E77" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J77">
         <v>1</v>
@@ -3206,19 +3190,19 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C78" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D78" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E78" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J78">
         <v>1</v>
@@ -3226,19 +3210,19 @@
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B79" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D79" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E79" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -3246,19 +3230,19 @@
     </row>
     <row r="80" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D80" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E80" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J80">
         <v>1</v>
@@ -3266,16 +3250,16 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B81" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D81" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E81" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="J81">
         <v>1</v>
@@ -3283,19 +3267,19 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B82" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C82" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D82" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E82" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J82">
         <v>1</v>
@@ -3303,19 +3287,19 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B83" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C83" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D83" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E83" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -3323,19 +3307,19 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B84" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C84" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="D84" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="E84" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -3343,19 +3327,19 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="B85" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C85" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D85" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E85" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="J85">
         <v>1</v>
@@ -3363,16 +3347,16 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B86" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D86" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E86" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J86">
         <v>1</v>
@@ -3380,19 +3364,19 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B87" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E87" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="J87">
         <v>1</v>
@@ -3400,19 +3384,19 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="B88" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C88" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D88" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="E88" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J88">
         <v>1</v>
@@ -3420,19 +3404,19 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C89" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D89" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E89" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -3440,16 +3424,16 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B90" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E90" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="J90">
         <v>1</v>
@@ -3457,19 +3441,19 @@
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B91" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C91" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D91" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E91" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J91">
         <v>1</v>
@@ -3477,16 +3461,16 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D92" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="J92">
         <v>1</v>
@@ -3494,19 +3478,19 @@
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C93" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D93" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E93" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J93">
         <v>1</v>
@@ -3514,19 +3498,19 @@
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B94" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C94" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="D94" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E94" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -3534,19 +3518,19 @@
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="B95" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C95" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D95" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E95" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J95">
         <v>1</v>
@@ -3554,16 +3538,16 @@
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B96" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D96" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E96" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="J96">
         <v>1</v>
@@ -3571,19 +3555,19 @@
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B97" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C97" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D97" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E97" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -3591,16 +3575,16 @@
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="B98" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D98" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E98" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="J98">
         <v>1</v>
@@ -3608,19 +3592,19 @@
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B99" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C99" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D99" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E99" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -3628,16 +3612,16 @@
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B100" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D100" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E100" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="J100">
         <v>1</v>
@@ -3645,19 +3629,19 @@
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B101" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C101" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D101" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E101" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J101">
         <v>1</v>
@@ -3665,19 +3649,19 @@
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B102" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C102" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D102" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E102" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J102">
         <v>1</v>
@@ -3685,19 +3669,19 @@
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C103" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D103" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E103" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="J103">
         <v>1</v>
@@ -3705,16 +3689,16 @@
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B104" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D104" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E104" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -3722,19 +3706,19 @@
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C105" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D105" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E105" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J105">
         <v>1</v>
@@ -3760,107 +3744,107 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -3884,69 +3868,69 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D5">
         <v>81260859</v>
@@ -3973,55 +3957,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="10.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
